--- a/results/Int Task Remove ACC 0.1/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.1/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.0037276531000379975 +/- 0.001138579653639833</t>
+          <t>-0.002776721186762998 +/- 0.0008513894745378149</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.00182578927348801 +/- 0.0012932674020540162</t>
+          <t>-0.0026245720806389984 +/- 0.0006002180995838468</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.001255230125522999 +/- 0.0016844115500558611</t>
+          <t>-0.0004564473183719886 +/- 0.0011512168847791359</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.0011411182959299992 +/- 0.0008673833587669272</t>
+          <t>-0.0003042982122479998 +/- 0.0006319226978256361</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.001445416508177999 +/- 0.0007176858982165464</t>
+          <t>-0.002510460251045998 +/- 0.0005159627221852564</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.00513503233168503 +/- 0.0014257637743622454</t>
+          <t>0.008900722708254104 +/- 0.0016510106058737523</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.0006466337010269996 +/- 0.00017430869893327467</t>
+          <t>-0.0001521491061239999 +/- 0.0001863438374121835</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0004944845949029997 +/- 0.0014736683627090384</t>
+          <t>0.0012171928489920325 +/- 0.001337268606409077</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.013959680486877101 +/- 0.0028568501682198857</t>
+          <t>0.00026626093571703314 +/- 0.0026519920903086197</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.02601749714720423 +/- 0.002394838530041426</t>
+          <t>0.01666032712057821 +/- 0.0022809683302494927</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.0005705591479649996 +/- 0.001668878734764555</t>
+          <t>-0.00034233548877898867 +/- 0.0015816373439552565</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.0016736401673639989 +/- 0.0006632025779445609</t>
+          <t>-0.0007987828071509995 +/- 0.0006466337010269996</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.0055534423735260074 +/- 0.001051371240858527</t>
+          <t>0.0013693419551160213 +/- 0.0011436513030333377</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.008063902624572062 +/- 0.003426734311009583</t>
+          <t>0.012666413084823169 +/- 0.003150671493325054</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.0011791555724609993 +/- 0.0018435330264058585</t>
+          <t>0.002738683910232076 +/- 0.001538512621997492</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.006238113351084029 +/- 0.0009348197586492886</t>
+          <t>0.0016356028908330322 +/- 0.0013071768944419833</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0007607455306199995 +/- 0.0017513677342291692</t>
+          <t>-0.005287181437808997 +/- 0.0007878400599926876</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.0052111068847470075 +/- 0.0013719808898342712</t>
+          <t>0.0001521491061240221 +/- 0.0013415893562988722</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.001559528337770999 +/- 0.0012780751324770836</t>
+          <t>-0.004031951312285997 +/- 0.0013088360999684344</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00024056885965525644</t>
+          <t>-0.0003423354887789998 +/- 0.00011411182959299992</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.006960821605173084 +/- 0.0017517807439588582</t>
+          <t>-0.003575503993913998 +/- 0.0012052475859836204</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0014130221088631807</t>
+          <t>-0.0016736401673639989 +/- 0.001668445203458431</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.0003042982122479998 +/- 0.0012004361991676937</t>
+          <t>0.0014073792316470213 +/- 0.0007804596625592913</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.0012171928489919993 +/- 0.0010865619518513159</t>
+          <t>3.803727653099998e-05 +/- 0.0009838354626380695</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.0011411182959299992 +/- 0.0008333549752836216</t>
+          <t>0.004526435907189108 +/- 0.0015446131992580248</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0003042982122479998 +/- 0.0006085964244959996</t>
+          <t>-0.00019018638265499987 +/- 0.0005705591479649996</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.014111829593001113 +/- 0.00162673296160846</t>
+          <t>0.010726511981742137 +/- 0.0023497063844017687</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-0.0007987828071509995 +/- 0.0011341233560955052</t>
+          <t>-0.004450361354126997 +/- 0.0018246002214091029</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>-0.0004944845949029997 +/- 0.0015502231930250752</t>
+          <t>-0.0024343856979839986 +/- 0.0013415893562988368</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00038037276530999975 +/- 0.0009471205475837657</t>
+          <t>0.003651578546976064 +/- 0.002028496253476388</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>7.607455306199996e-05 +/- 0.00047508543160124247</t>
+          <t>0.0003423354887789998 +/- 0.0004320204142868173</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.0012171928489919993 +/- 0.0005843397297731858</t>
+          <t>3.803727653099998e-05 +/- 0.0004944845949029997</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,122 +1046,122 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.0027767211867630315 +/- 0.0014439142560747544</t>
+          <t>-0.0035374667173829976 +/- 0.0010630040785456045</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.010726511981742104 +/- 0.0015939388999434566</t>
+          <t>-0.009433244579688072 +/- 0.0021436291827471275</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.0004564473183719997 +/- 0.00047508543160124247</t>
+          <t>-3.803727653099998e-05 +/- 0.00035884294910827326</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.0007607455306199995 +/- 0.0008673833587669272</t>
+          <t>-0.001293267402053999 +/- 0.0006846709775579996</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.0014073792316469992 +/- 0.0019022441612856378</t>
+          <t>0.004184100418410108 +/- 0.0008158086949230501</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>-0.005781666032712107 +/- 0.000928608262893387</t>
+          <t>-0.006200076074552996 +/- 0.0009478840467384541</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.0032712057816659977 +/- 0.0008014951504642545</t>
+          <t>-0.0009128946367439994 +/- 0.0007832354614672417</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.00022822365918599984 +/- 0.0010918752449149615</t>
+          <t>0.0023202738683910764 +/- 0.001322581867684598</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.0016736401673639989 +/- 0.0012052475859836204</t>
+          <t>-0.006884747052111018 +/- 0.0015539519373005506</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0009509319132749994 +/- 0.0009199989823086873</t>
+          <t>-0.003042982122479998 +/- 0.0008505393600227333</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.0007607455306199995 +/- 0.0014926905188549545</t>
+          <t>0.0014454165081780434 +/- 0.0009889691898060497</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>-0.0073411943704831065 +/- 0.001483453784708999</t>
+          <t>-0.004031951312285997 +/- 0.0010234784364453074</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0034233548877899977 +/- 0.001595753287440305</t>
+          <t>0.0014073792316470213 +/- 0.000868216980640063</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.005743628756181019 +/- 0.0015257642540990306</t>
+          <t>0.002890833016356087 +/- 0.0007645397962054895</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.0004564473183719997 +/- 0.00044358705932637796</t>
+          <t>0.00011411182959299992 +/- 0.00017430869893327467</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.003233168505134998 +/- 0.0008376841211694563</t>
+          <t>0.002092050209205054 +/- 0.0005705591479650477</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.004146063141879009 +/- 0.0017877519969570158</t>
+          <t>0.0009128946367440327 +/- 0.001130929535741261</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.007531380753138073 +/- 0.002203537216882521</t>
+          <t>-0.0024724229745149984 +/- 0.0012982919867535817</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.004526435907189019 +/- 0.001763305741574648</t>
+          <t>-0.0037656903765689977 +/- 0.0011962103608608764</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-0.0007987828071509995 +/- 0.0006238577203064493</t>
+          <t>0.0013313046785849991 +/- 0.00025516180800682</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>-0.00038037276530999975 +/- 0.0006364853758342082</t>
+          <t>-7.607455306199996e-05 +/- 0.0005325218714339997</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00038037276530999975</t>
+          <t>-0.0006846709775579996 +/- 0.00028464491340995826</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.0036135412704449976 +/- 0.0014053216585706329</t>
+          <t>0.0012171928489919993 +/- 0.0006761654178254464</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.005515405096995019 +/- 0.0011187098645761113</t>
+          <t>0.003993914035755108 +/- 0.0011442836786984528</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1171,92 +1171,92 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.0004184100418409997 +/- 0.0007306722218447449</t>
+          <t>-0.0013693419551159991 +/- 0.0005941612533972287</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.001787751996956999 +/- 0.0012154085438318971</t>
+          <t>0.0012932674020540325 +/- 0.0008193480117359773</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.003157093952072998 +/- 0.0015962065620659615</t>
+          <t>0.0015214910612400435 +/- 0.0013714535091152804</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>-0.0005705591479649996 +/- 0.0004885976636996955</t>
+          <t>0.0007227082540889995 +/- 0.00039712082574782954</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.0017116774438949989 +/- 0.0011568586021867924</t>
+          <t>-0.0024724229745149984 +/- 0.001495111754053506</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.004754659566375008 +/- 0.0012644176598398456</t>
+          <t>0.009471281856219104 +/- 0.0010818914152398434</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-0.005020920502092074 +/- 0.002004098877492525</t>
+          <t>-0.001977938379611999 +/- 0.0012004361991676937</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-0.009623430962343105 +/- 0.0012735389153885912</t>
+          <t>-0.001787751996956999 +/- 0.0009009295764417562</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>-3.803727653099998e-05 +/- 0.00026626093571699986</t>
+          <t>-3.803727653099998e-05 +/- 0.00011411182959299992</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>-0.009319132750095105 +/- 0.0013528656708846369</t>
+          <t>-0.0006466337010269996 +/- 0.0010213557688929181</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>-0.0003423354887789998 +/- 0.001159357219789122</t>
+          <t>-0.001293267402053999 +/- 0.0010234784364453074</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-0.001255230125522999 +/- 0.0005392714674308739</t>
+          <t>0.0002662609357169998 +/- 0.0003423354887789998</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-0.011297071129707103 +/- 0.001726825327168664</t>
+          <t>-0.0023583111449219985 +/- 0.0005843397297731858</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>-0.00201597565614301 +/- 0.0011791555724610197</t>
+          <t>-0.001749714720425999 +/- 0.0009033352671767054</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-0.010232027386839104 +/- 0.0015446131992580248</t>
+          <t>-0.0016356028908329988 +/- 0.0009630269228734902</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.00011411182959299992 +/- 0.00017430869893327467</t>
+          <t>-3.803727653099998e-05 +/- 0.00020483700293398428</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>-0.001293267402053999 +/- 0.0008539347402298748</t>
+          <t>0.0007607455306199995 +/- 0.0006133326548724582</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>-0.0010650437428679992 +/- 0.00044358705932637796</t>
+          <t>0.0004184100418409997 +/- 0.0007105949673742566</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.0004564473183719997 +/- 0.0006319226978256361</t>
+          <t>-0.00019018638265499987 +/- 0.00019018638265499987</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>-0.0066945606694561064 +/- 0.001286537430603848</t>
+          <t>-0.0012171928489919993 +/- 0.0011883225067944574</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1281,37 +1281,37 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>-0.0007227082540889995 +/- 0.0005498985277596351</t>
+          <t>0.0003042982122479998 +/- 0.0003316012889722805</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>-0.007721567135793106 +/- 0.0009779353466856072</t>
+          <t>-0.001445416508177999 +/- 0.0009128946367439994</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>-0.008862685431723106 +/- 0.0020487231661460766</t>
+          <t>-0.0011030810193989992 +/- 0.001159357219789122</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>-0.0021681247622669987 +/- 0.0006599220834118405</t>
+          <t>0.0019018638265500543 +/- 0.0006133326548725064</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>-0.001521491061239999 +/- 0.0020554212379012785</t>
+          <t>-0.0004944845949029997 +/- 0.0009009295764417562</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>-0.005439330543933085 +/- 0.0018482359244209078</t>
+          <t>-0.0034233548877899977 +/- 0.0008333549752836216</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.00038037276530999975 +/- 0.0009622754386210257</t>
+          <t>0.0014834537847090434 +/- 0.0010409990249832153</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.0018278750952018252 +/- 0.0010046386868448483</t>
+          <t>0.0006854531607006665 +/- 0.0008308234664611919</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.0028941355674029 +/- 0.001230426079314818</t>
+          <t>-3.8080731150036404e-05 +/- 0.001459540586194729</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.0006092916984006047 +/- 0.001132221534449248</t>
+          <t>0.0027418126428027214 +/- 0.0011270867164469719</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.007806549885757819 +/- 0.0015998439861081588</t>
+          <t>0.008948971820258922 +/- 0.0019286301998630113</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.005635948210205621 +/- 0.0013495845503937187</t>
+          <t>-0.004531607006854554 +/- 0.0006693981656986357</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0017897943640517889 +/- 0.001404864184744632</t>
+          <t>0.009405940594059381 +/- 0.0011927235158694378</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.8080731150036404e-05 +/- 0.00011424219345010921</t>
+          <t>0.00038080731150036407 +/- 0.00029497207511098607</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.0019421172886519456 +/- 0.0013349998585649725</t>
+          <t>-0.00525514089870528 +/- 0.001622793278953726</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.051370906321401386 +/- 0.003966433092756409</t>
+          <t>0.04207920792079206 +/- 0.0047356570128452655</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.059824828636709834 +/- 0.004599578554272056</t>
+          <t>0.04611576542269611 +/- 0.0030485997805979365</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-0.017060167555217054 +/- 0.0023585472303430375</t>
+          <t>-0.015841584158415835 +/- 0.0020940939961717354</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-0.0050266565118050055 +/- 0.0010470469980858655</t>
+          <t>0.001180502665651173 +/- 0.0009083671319022517</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-0.0008377760853008453 +/- 0.0010743896404924755</t>
+          <t>0.00019040365575017092 +/- 0.001722074494226213</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.013975628332063995 +/- 0.001737165990549442</t>
+          <t>0.010967250571210962 +/- 0.0011270867164469847</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.008758568164508772 +/- 0.001063536941642715</t>
+          <t>0.014013709063213985 +/- 0.0022515987051172173</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.0020182787509520407 +/- 0.0008857352132226245</t>
+          <t>0.006930693069306914 +/- 0.0014022812368257444</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.0014089870525514248 +/- 0.0010777586974931306</t>
+          <t>-0.0014089870525514359 +/- 0.001455560918021063</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-0.0012566641279512347 +/- 0.0015889296302380063</t>
+          <t>-0.003198781416603236 +/- 0.0015155939636049096</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-0.001904036557501898 +/- 0.0007616146230007614</t>
+          <t>-0.0022086824067022114 +/- 0.0017182809097758686</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3.8080731150036404e-05 +/- 0.00011424219345010921</t>
+          <t>0.0004569687738004369 +/- 0.00033198011755830023</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.0040365575019040145 +/- 0.0028810784949547235</t>
+          <t>-0.0007616146230007947 +/- 0.002724835311500113</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-0.0035795887281035777 +/- 0.0018671211991060457</t>
+          <t>0.0014089870525513914 +/- 0.0011173953351958242</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.0015613099771515926 +/- 0.0009083671319022678</t>
+          <t>0.0005331302361005208 +/- 0.0011449578353673196</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.0022848438690022954 +/- 0.0009171054515454967</t>
+          <t>0.0033130236100533004 +/- 0.0012635689278779176</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.0012185833968012317 +/- 0.001225702737199619</t>
+          <t>0.0005331302361005097 +/- 0.0015719548698058061</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.000533130236100543 +/- 0.0004240490756154155</t>
+          <t>0.00026656511805024375 +/- 0.0006822723864116045</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.010396039603960416 +/- 0.0014354970925339284</t>
+          <t>-0.000875856816450904 +/- 0.0013086702419984333</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-0.012300076161462292 +/- 0.0020861151446766707</t>
+          <t>-0.003655750190403684 +/- 0.0024924703993836447</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.003198781416603169 +/- 0.0014370115966574957</t>
+          <t>0.0028560548362528302 +/- 0.0018829756763253987</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.0009139375476009071 +/- 0.0014268845388571932</t>
+          <t>0.003617669459253603 +/- 0.0011706341316785427</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-7.616146230007281e-05 +/- 0.00033198011755830023</t>
+          <t>-3.8080731150036404e-05 +/- 0.0005762660300998054</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.0006473724295506522 +/- 0.0007032058382566513</t>
+          <t>0.0007235338918506918 +/- 0.00046483456267072226</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,122 +1491,122 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.002703731911652729 +/- 0.0015742594522920323</t>
+          <t>0.0042269611576541966 +/- 0.0008922600543686216</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.012757044935262751 +/- 0.001980564146831057</t>
+          <t>-0.005597867479055607 +/- 0.0020009603435521095</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.0005331302361005208 +/- 0.0003490156660286285</t>
+          <t>0.0009520182787509102 +/- 0.00035108699380397875</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.00022848438690022954 +/- 0.0005699401960051627</t>
+          <t>-0.0014851485148515086 +/- 0.0006245704290501469</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.004112718964204143 +/- 0.0010878032640583226</t>
+          <t>-0.0012566641279512902 +/- 0.0003827066116192385</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.00022848438690024065 +/- 0.0008202840528765418</t>
+          <t>0.0007616146230007392 +/- 0.0019342612489261705</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.00011424219345012032 +/- 0.0005398875429839207</t>
+          <t>0.0008377760853008232 +/- 0.0009603594983182312</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.002056359482102066 +/- 0.0010525723504253887</t>
+          <t>0.004379284082254353 +/- 0.0009966681133512878</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.004798172124904787 +/- 0.0012185833968012005</t>
+          <t>-0.005407463823305425 +/- 0.00143296936193652</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0016374714394516432 +/- 0.0009641271059536985</t>
+          <t>0.0004569687738004369 +/- 0.001800699225824339</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.001980198019801982 +/- 0.0013279204702332595</t>
+          <t>0.00453160700685451 +/- 0.001367199015309682</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.004036557501904037 +/- 0.0015346109428491885</t>
+          <t>0.0012185833968011983 +/- 0.0013814438040530904</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-0.002361005331302346 +/- 0.0011270867164469838</t>
+          <t>-0.004074638233054107 +/- 0.001415148832906486</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.004722010662604725 +/- 0.0008549102940077392</t>
+          <t>-0.0038842345773039133 +/- 0.001776375291651271</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.000799695354150809 +/- 0.0008069162262154357</t>
+          <t>0.0007996953541507645 +/- 0.00046483456267072226</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>-0.004036557501904026 +/- 0.0007654132232384638</t>
+          <t>-0.003122619954303163 +/- 0.0014530680905056347</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.008948971820258977 +/- 0.0014069271288584268</t>
+          <t>0.011119573495811098 +/- 0.0017013181952542649</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.0063594821020563795 +/- 0.0009790525614761956</t>
+          <t>0.0030464584920030123 +/- 0.0016511411567919842</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.002437166793602452 +/- 0.00170472424109666</t>
+          <t>0.0006092916984005825 +/- 0.0012880071991841495</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-0.0015232292460015007 +/- 0.0007021739876080056</t>
+          <t>0.002437166793602441 +/- 0.0003490156660286092</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>-0.0009900990099009689 +/- 0.0006639602351166309</t>
+          <t>0.0009139375476008849 +/- 0.0008202840528765253</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>-0.0014851485148515199 +/- 0.00011424219345014252</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-0.0010281797410510163 +/- 0.000852362120548341</t>
+          <t>0.00099009900990098 +/- 0.0015811530458512285</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.0014851485148515086 +/- 0.000669398165698666</t>
+          <t>0.00373191165270369 +/- 0.0011774276339482363</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1616,92 +1616,92 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-0.0002665651180502659 +/- 0.0005661107672246191</t>
+          <t>-0.00022848438690024065 +/- 0.0006187386446790583</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-0.002475247524752466 +/- 0.0011199879032637028</t>
+          <t>-0.003122619954303141 +/- 0.0012947448591013038</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-0.00015232292460016784 +/- 0.0013213519857500013</t>
+          <t>0.00476009139375474 +/- 0.0017136329017517335</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.0007996953541508312 +/- 0.0008246918441625296</t>
+          <t>0.0004569687738004369 +/- 0.000865027927768512</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-0.005140898705255114 +/- 0.0014273925981714596</t>
+          <t>-0.004112718964204154 +/- 0.00142281353330308</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.0019421172886519677 +/- 0.0006009038019062759</t>
+          <t>0.006169078446306142 +/- 0.0014430537183165732</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-0.0011424219345011366 +/- 0.000851511034843801</t>
+          <t>0.0009900990099009576 +/- 0.0017132097302668633</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-0.0005331302361005319 +/- 0.0005948400362457575</t>
+          <t>0.004722010662604703 +/- 0.0005439016320291749</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.00019040365575018203 +/- 0.00019040365575018203</t>
+          <t>-3.8080731150036404e-05 +/- 0.00011424219345010921</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.007311500380807334 +/- 0.0009603594983182542</t>
+          <t>0.0034272658035034097 +/- 0.0010218132418125308</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>-0.004455445544554459 +/- 0.0007813512767967707</t>
+          <t>0.0050266565118050055 +/- 0.0013814438040530873</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-0.00034272658035032765 +/- 0.0006473724295506189</t>
+          <t>0.002779893373952769 +/- 0.0009489669302648202</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.005597867479055618 +/- 0.002093055001319317</t>
+          <t>0.013290175171363272 +/- 0.001398657096131521</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>-0.003313023610053323 +/- 0.0012286569539148185</t>
+          <t>0.0031226199543031075 +/- 0.0007951490105796158</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.0017136329017517383 +/- 0.0011069643452969284</t>
+          <t>0.0040365575019040145 +/- 0.0015627025535935386</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.00026656511805025487 +/- 0.00029742001812286026</t>
+          <t>-7.616146230007281e-05 +/- 0.00022848438690021842</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.001675552170601702 +/- 0.0005948400362457375</t>
+          <t>0.0022467631378522146 +/- 0.000770135126281679</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.0006092916984006159 +/- 0.0005165521693164911</t>
+          <t>0.0027037319116526848 +/- 0.0010281797410510328</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.0004950495049504955 +/- 0.0005123238403303068</t>
+          <t>0.0007996953541507645 +/- 0.00046483456267072226</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.004303122619954314 +/- 0.0008176279723375416</t>
+          <t>0.008377760853008375 +/- 0.001560845508904736</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1726,37 +1726,37 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.0012947448591013378 +/- 0.0005699401960051627</t>
+          <t>0.003922315308453894 +/- 0.0009019588181513321</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>-0.008035034272658014 +/- 0.0015557272060788782</t>
+          <t>-0.0019421172886519567 +/- 0.0011606816949069477</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>-0.0007996953541507867 +/- 0.0005505267438995162</t>
+          <t>0.003808073115003796 +/- 0.0011167462527505775</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.001789794364051822 +/- 0.0010366075848298698</t>
+          <t>0.0006854531607006553 +/- 0.0005596701620981882</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>-0.0002665651180502659 +/- 0.0005911719229344997</t>
+          <t>0.003160700685453133 +/- 0.0012520397732500926</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.0031607006854531662 +/- 0.0010911309049424476</t>
+          <t>0.001180502665651162 +/- 0.001042188285103121</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>-0.001104341203351089 +/- 0.0006245704290501503</t>
+          <t>-0.0012185833968012538 +/- 0.0012138139718590253</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.007925673113386367 +/- 0.00110495277090129</t>
+          <t>0.0020477815699659007 +/- 0.001574557413122983</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,157 +1776,157 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.0029199848312475908 +/- 0.001842628837809069</t>
+          <t>-0.001858172165339389 +/- 0.0013928227282674734</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.007773985589685173 +/- 0.0021602162106372654</t>
+          <t>-0.0037542662116040516 +/- 0.0018379402072131346</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.004512703830109943 +/- 0.0018300991296190659</t>
+          <t>0.002844141069397066 +/- 0.0023757990303643743</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.00629503223359873 +/- 0.0016106758120284469</t>
+          <t>-0.004929844520288174 +/- 0.0012803900656908854</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.005650360257868747 +/- 0.001630640879787638</t>
+          <t>-0.004133485020857008 +/- 0.002471913308719354</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0006446719757299158 +/- 0.0002961793582065614</t>
+          <t>3.79218809253179e-05 +/- 0.0007854499498372425</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.009290860826696955 +/- 0.0022257915192763346</t>
+          <t>-0.002654531664770532 +/- 0.0011502275986426168</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.02184300341296923 +/- 0.003638129679245037</t>
+          <t>0.024421691315889303 +/- 0.002735637284318767</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.032688661357603274 +/- 0.003962065342922725</t>
+          <t>0.049146757679180905 +/- 0.005025758136375979</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.0041714069017822816 +/- 0.0013245543569641836</t>
+          <t>0.009177095183921147 +/- 0.0017689653074995381</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.00022753128555172975 +/- 0.001431017236565263</t>
+          <t>-0.0036405005688281977 +/- 0.0012485458955748202</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.005915813424345784 +/- 0.0017963927618243473</t>
+          <t>3.79218809253179e-05 +/- 0.0018379402072131227</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.027493363670838024 +/- 0.004049836731087224</t>
+          <t>0.017747440273037585 +/- 0.002754496745898337</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-0.006370875995449421 +/- 0.002242206370738653</t>
+          <t>-0.019302237390974565 +/- 0.004089413774163191</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.005195297686765221 +/- 0.0017047983915805072</t>
+          <t>-0.0008342813803564386 +/- 0.001736143062913842</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.0029579067121728642 +/- 0.0014370341540763205</t>
+          <t>-0.0009859689040575992 +/- 0.0014410314751611597</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.0004171406901782748 +/- 0.001239877339724808</t>
+          <t>-0.005612438376943451 +/- 0.0010287948400645214</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.006408797876374617 +/- 0.0013720176348218113</t>
+          <t>0.002237390974592357 +/- 0.0009510759350765668</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.0003033750474022989 +/- 0.0002837813717689414</t>
+          <t>-0.00011376564277588707 +/- 0.0002961793582065614</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.012703830109973401 +/- 0.0014214383628359105</t>
+          <t>0.012779673871824094 +/- 0.0018658952749552504</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.003981797497155793 +/- 0.0010624896265545667</t>
+          <t>0.009101251422070567 +/- 0.00222417569944865</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.0028062191884716927 +/- 0.001410775520495891</t>
+          <t>-0.0010618126659082128 +/- 0.0016160239478697324</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.0028441410693970104 +/- 0.0011657509403821917</t>
+          <t>-0.0047402351156617065 +/- 0.0009779140658496548</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.0018960940462646402 +/- 0.001608889149457428</t>
+          <t>-0.0007584376185058361 +/- 0.0016616535684646782</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.0006825938566552226 +/- 0.0005825669888410018</t>
+          <t>0.00026545316647706984 +/- 0.0002961793582065614</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.007963594994311674 +/- 0.001535719130171919</t>
+          <t>0.016571861964353472 +/- 0.0023070096585900875</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-0.004133485020857086 +/- 0.0026297669241692697</t>
+          <t>0.0007205157375806293 +/- 0.0022591385678584013</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.0026924535456958167 +/- 0.0019664606996532626</t>
+          <t>-0.0009101251422070189 +/- 0.0019276852525049529</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.017330299582859265 +/- 0.0021919372038859855</t>
+          <t>0.009632157755024661 +/- 0.001592718998862337</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0009480470231323035 +/- 0.0007244965178059456</t>
+          <t>0.0005688282138794354 +/- 0.0003496224670949307</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.0019719378081152427 +/- 0.0008273577637190587</t>
+          <t>0.0016685627607129438 +/- 0.0010885627678731407</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1936,122 +1936,122 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.014979142965491032 +/- 0.003182954048956132</t>
+          <t>0.010656048540007613 +/- 0.002038279052010118</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.002919984831247657 +/- 0.002544159744819041</t>
+          <t>-0.008039438756162276 +/- 0.0016160239478697391</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>-0.0001516875237012161 +/- 0.0006390708967141615</t>
+          <t>0.0004550625711035483 +/- 0.0003305952934046932</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.0013651877133105338 +/- 0.0009472882818958338</t>
+          <t>-0.0034129692832764237 +/- 0.0009132798315352306</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.002616609783845225 +/- 0.0016394362018367266</t>
+          <t>0.00018960940462648957 +/- 0.0024058736330014275</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.003450891164201697 +/- 0.000666605833570235</t>
+          <t>0.00451270383011001 +/- 0.0017497568441500707</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-0.0011755783086841664 +/- 0.0009203383465689608</t>
+          <t>0.0005688282138794354 +/- 0.0005688282138794354</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-7.584376185062469e-05 +/- 0.0013964317511962097</t>
+          <t>-0.003261281759575252 +/- 0.001165133977682014</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.010200985968904019 +/- 0.0013824593199513217</t>
+          <t>0.0045127038301099875 +/- 0.0012854343008478065</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0004929844520287552 +/- 0.002006995619628252</t>
+          <t>-0.001971937808115265 +/- 0.0010699079241309089</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-0.008115282518012945 +/- 0.001315840088956955</t>
+          <t>0.002957906712172942 +/- 0.0017278400834121483</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.0072430792567310665 +/- 0.0019591340694864734</t>
+          <t>0.005384907091391777 +/- 0.0027753013975778604</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.003450891164201686 +/- 0.001511651985437607</t>
+          <t>0.00037921880925297915 +/- 0.0011120878497243136</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.006863860447478132 +/- 0.0015492376348741439</t>
+          <t>0.013234736442927586 +/- 0.0013824593199513193</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.0002654531664770032 +/- 0.0007002724805695498</t>
+          <t>0.0004550625711035483 +/- 0.00044224132687490156</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.008608266970041667 +/- 0.0017871629378760974</t>
+          <t>-0.001706484641638184 +/- 0.0009327549394196997</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>-0.007394766780432371 +/- 0.0019130827843199716</t>
+          <t>0.004474781949184725 +/- 0.001659921776885814</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-0.009783845278725879 +/- 0.0013004496169497332</t>
+          <t>-0.0007584376185058361 +/- 0.0013777703545381056</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-0.009935532802427061 +/- 0.0015981272283432085</t>
+          <t>-0.00572620401971935 +/- 0.0013402045541958316</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.0015168752370117167 +/- 0.0006114719566400403</t>
+          <t>0.00026545316647708095 +/- 0.0007780919426880408</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>-0.0011755783086841553 +/- 0.000548230272840389</t>
+          <t>0.000492984452028844 +/- 0.0004502973866908791</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>-0.000492984452028844 +/- 0.0003811101866181785</t>
+          <t>0.0010997345468335639 +/- 0.0007479364020976999</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.0006825938566552448 +/- 0.002157218453292064</t>
+          <t>-0.012135001896094021 +/- 0.00197047873443558</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.009632157755024595 +/- 0.0022059976598026625</t>
+          <t>-0.010200985968904019 +/- 0.0015492376348741435</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2061,107 +2061,107 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-0.0004171406901782637 +/- 0.0005213396695057835</t>
+          <t>0.00018960940462647846 +/- 0.0003885836467940874</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.0012514220705346691 +/- 0.001498274271151937</t>
+          <t>0.004398938187334123 +/- 0.0015469152866417286</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-0.0069017823284035495 +/- 0.001863967497526667</t>
+          <t>0.008266970041714106 +/- 0.002143844372408438</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.0002654531664770143 +/- 0.0006356865610253962</t>
+          <t>-0.0004171406901782193 +/- 0.00046289554856781016</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.002995828593098171 +/- 0.0010097479678190663</t>
+          <t>0.010769814182783489 +/- 0.0016460018516655623</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.0030716723549487623 +/- 0.0022591385678584065</t>
+          <t>-0.006295032233598752 +/- 0.0014900934929380793</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.003261281759575241 +/- 0.003137219246104885</t>
+          <t>-0.005422828972316995 +/- 0.001507841892458907</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.009252938945771672 +/- 0.001348228201337214</t>
+          <t>0.005802047781570008 +/- 0.0015078418924589503</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.00011376564277583156 +/- 0.00029617935820651164</t>
+          <t>-7.584376185059139e-05 +/- 0.00015168752370118277</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.014524080394387517 +/- 0.0013990039245883163</t>
+          <t>-0.0004929844520287774 +/- 0.0013678186421593956</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.0059916571861963865 +/- 0.001969018579559674</t>
+          <t>-0.0006825938566552558 +/- 0.0016248983910222756</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-0.0011755783086841664 +/- 0.000492984452028844</t>
+          <t>-3.792188092528459e-05 +/- 0.0006219650916517628</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.007698141827834593 +/- 0.0026656142238589194</t>
+          <t>-0.008039438756162276 +/- 0.0020687420094024963</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.0067500948047022665 +/- 0.0015338451586011782</t>
+          <t>-0.0019340159271899581 +/- 0.0010238907849829306</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.008494501327265758 +/- 0.001628434626741299</t>
+          <t>0.007698141827834704 +/- 0.0015078418924589318</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>3.792188092527349e-05 +/- 0.0002042155785792105</t>
+          <t>3.7921880925295694e-05 +/- 0.00026545316647706984</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.0044368600682593295 +/- 0.0008142173133706353</t>
+          <t>7.584376185060249e-05 +/- 0.0006067500948047158</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.003450891164201697 +/- 0.000728455544645392</t>
+          <t>-0.00015168752370116058 +/- 0.0004856370297635701</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>-0.00011376564277588707 +/- 0.0001737798898352695</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.0007205157375805404 +/- 0.0005482302728403675</t>
+          <t>0.0028062191884717703 +/- 0.0005675627435379778</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.018430034129692786 +/- 0.00137985630630719</t>
+          <t>-0.003223359878649945 +/- 0.001006895566731275</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2171,37 +2171,37 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.00018960940462641184 +/- 0.00045663991576760146</t>
+          <t>0.0021236253318164698 +/- 0.0005143974200322521</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.003981797497155814 +/- 0.0006622771784821092</t>
+          <t>0.005839969662495304 +/- 0.0014005449611391404</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.00511945392491463 +/- 0.0014613461409175347</t>
+          <t>0.0013272658323852937 +/- 0.0009327549394196997</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>-0.0001516875237012161 +/- 0.0007990636141716146</t>
+          <t>0.0010238907849829727 +/- 0.0011632811262933683</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>-0.0010238907849829837 +/- 0.001409245671297846</t>
+          <t>0.002275312855517642 +/- 0.0008647519340911337</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.01171786120591578 +/- 0.0016039655656091406</t>
+          <t>-0.0036405005688281756 +/- 0.0012252934714754287</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.0013651877133105338 +/- 0.0008680715314569353</t>
+          <t>0.0003033750474023877 +/- 0.0011477243800092128</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.0019999999999999905 +/- 0.001454001071882167</t>
+          <t>-0.0019591836734693113 +/- 0.0018597201224317514</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.017387755102040846 +/- 0.0021302838123591432</t>
+          <t>-0.021346938775510138 +/- 0.003027294961761428</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0006530612244897927 +/- 0.0016749620023414822</t>
+          <t>-0.002897959183673404 +/- 0.0014309018892210645</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.015632653061224456 +/- 0.0012653061224489949</t>
+          <t>0.011224489795918424 +/- 0.002504473299043652</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.003224489795918317 +/- 0.001371452866645816</t>
+          <t>0.01073469387755105 +/- 0.0020330464335366967</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.004163265306122432 +/- 0.0028148472897251606</t>
+          <t>0.00522448979591843 +/- 0.0022637427957326066</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0001224489795918382 +/- 0.0005179011240999867</t>
+          <t>0.00020408163265307478 +/- 0.0003763079370323492</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.010816326530612241 +/- 0.002381729707901243</t>
+          <t>0.004163265306122499 +/- 0.001955779355218136</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.03391836734693874 +/- 0.004506277725807342</t>
+          <t>0.02359183673469394 +/- 0.003538566008439716</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.024163265306122415 +/- 0.003845409212510675</t>
+          <t>0.04175510204081638 +/- 0.0026392103118901885</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.0071020408163265155 +/- 0.002569808365501593</t>
+          <t>0.013346938775510252 +/- 0.0023592401659785467</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-0.0015918367346938966 +/- 0.0017551020408163474</t>
+          <t>0.009306122448979626 +/- 0.001850740252857884</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.005387755102040781 +/- 0.002079630890262372</t>
+          <t>0.006653061224489864 +/- 0.0016932627357299215</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.02265306122448977 +/- 0.002325098019367513</t>
+          <t>0.03118367346938781 +/- 0.0027392590588673593</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.03493877551020406 +/- 0.0026777501170378647</t>
+          <t>0.029224489795918417 +/- 0.003000485869304336</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.007591836734693891 +/- 0.0019335051889513327</t>
+          <t>-0.002530612244897901 +/- 0.002127153342170665</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.006734693877551034 +/- 0.0013690212107141239</t>
+          <t>0.00016326530612249536 +/- 0.002690164416862693</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.004857142857142815 +/- 0.0014192113184255976</t>
+          <t>0.014530612244898022 +/- 0.001067485455560994</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.0008163265306122547 +/- 0.001548870690694735</t>
+          <t>-0.003102040816326457 +/- 0.0008600533675798258</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.000612244897959191 +/- 0.0002738042421428347</t>
+          <t>0.00016326530612247313 +/- 0.0005227040193822467</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.007877551020408168 +/- 0.0024081632653061183</t>
+          <t>-0.0025306122448978895 +/- 0.00190398429219438</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.015346938775510178 +/- 0.002720952377550867</t>
+          <t>0.014734693877551075 +/- 0.001820334948651245</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.0011020408163265438 +/- 0.0016534391102472927</t>
+          <t>0.002326530612244937 +/- 0.0012913707771066347</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.0001224489795918382 +/- 0.0020165909105364526</t>
+          <t>-0.0006530612244897372 +/- 0.0011281857111089721</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00583673469387751 +/- 0.0018439766527472087</t>
+          <t>0.0017959183673469602 +/- 0.0013805334306357523</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.0002448979591836764 +/- 0.001227207867622293</t>
+          <t>0.0011836734693877805 +/- 0.0010398154451311788</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>-0.0015918367346938966 +/- 0.00333322226664887</t>
+          <t>0.005510204081632697 +/- 0.003157664561198609</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.014979591836734673 +/- 0.003239952591423047</t>
+          <t>0.019142857142857194 +/- 0.0031587195777870694</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.015306122448979553 +/- 0.001959608797413542</t>
+          <t>0.013469387755102091 +/- 0.0017316900763752392</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.019959183673469372 +/- 0.0022611655484839994</t>
+          <t>0.012897959183673513 +/- 0.002082832787293588</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-0.0001224489795918382 +/- 0.00044897959183674006</t>
+          <t>0.00020408163265308587 +/- 0.0004914936562772147</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.081632653061273e-05 +/- 0.0008648824530782588</t>
+          <t>-0.0013877551020407219 +/- 0.0006108828386569773</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,122 +2381,122 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.016081632653061194 +/- 0.002646459604481228</t>
+          <t>0.015183673469387815 +/- 0.0031658317436188154</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.020448979591836714 +/- 0.0029851778780778018</t>
+          <t>0.010448979591836782 +/- 0.0032663263712232795</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.0005714285714285783 +/- 0.001082979523381368</t>
+          <t>-0.0004081632653060607 +/- 0.0005772300254583738</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.0013061224489796075 +/- 0.0005097957549713039</t>
+          <t>0.0006938775510204387 +/- 0.0008951719265086083</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.001795918367346938 +/- 0.001624469285072018</t>
+          <t>0.003959183673469435 +/- 0.0014378706084741835</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.011469387755102024 +/- 0.002340808319826865</t>
+          <t>0.008326530612244965 +/- 0.0025107847345680993</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.0009387755102040929 +/- 0.0009493635387439302</t>
+          <t>0.0013061224489796185 +/- 0.0008122346425360026</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.004448979591836777 +/- 0.0015855448652697974</t>
+          <t>0.0007755102040816753 +/- 0.001564389216060126</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.014163265306122419 +/- 0.0028979591836734756</t>
+          <t>0.009510204081632678 +/- 0.0013665852279822804</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-0.010367346938775524 +/- 0.002295895691498025</t>
+          <t>-0.0018367346938774954 +/- 0.002416450631120911</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-0.0005714285714285783 +/- 0.002017829729683008</t>
+          <t>-0.013673469387755044 +/- 0.0016853732915969653</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.006938775510204054 +/- 0.0028745823447606494</t>
+          <t>0.017020408163265367 +/- 0.001516808504168304</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-0.0010612244897959312 +/- 0.0012672795670416498</t>
+          <t>0.0015102040816326935 +/- 0.0013419822222672133</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.00824489795918366 +/- 0.0021035263227306583</t>
+          <t>4.4408920985006264e-17 +/- 0.0019057334742740549</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.0005306122448979656 +/- 0.00036734693877551463</t>
+          <t>0.0004897959183673528 +/- 0.00030544141932848864</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.0019999999999999905 +/- 0.0017739848009877917</t>
+          <t>0.004000000000000048 +/- 0.0014233139407479921</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>-0.002775510204081655 +/- 0.001700625849469353</t>
+          <t>-0.0027346938775509645 +/- 0.0022508270496264735</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-0.03212244897959186 +/- 0.0024219597876157938</t>
+          <t>-0.03771428571428568 +/- 0.0031202473230394026</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-0.002326530612244926 +/- 0.0014145080368296867</t>
+          <t>-0.021795918367346866 +/- 0.00164485238200899</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-0.00016326530612245093 +/- 0.0008792105807566643</t>
+          <t>0.00020408163265309698 +/- 0.0007128264978192789</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.0012653061224489949 +/- 0.0005900747875429034</t>
+          <t>0.0006938775510204387 +/- 0.0006594079355674612</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>-0.0011836734693877692 +/- 0.0003850604543696619</t>
+          <t>0.00044897959183674006 +/- 0.00021980264518916604</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.004897959183673428 +/- 0.002175169403179465</t>
+          <t>-0.004081632653061162 +/- 0.0018525397090465882</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.011183673469387733 +/- 0.0023532302539427726</t>
+          <t>0.0031428571428571916 +/- 0.0023450746811793073</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2506,147 +2506,147 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-0.0007346938775510293 +/- 0.0005097957549713039</t>
+          <t>0.00036734693877551463 +/- 0.00033904587195584385</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-0.00881632653061224 +/- 0.001818045506230233</t>
+          <t>0.003836734693877597 +/- 0.001818045506230233</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-0.011428571428571455 +/- 0.0014020868601892144</t>
+          <t>-0.009142857142857074 +/- 0.0029331010976688353</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>-0.0011428571428571566 +/- 0.0010130345833462046</t>
+          <t>-0.0017551020408162366 +/- 0.0005179011240999867</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.0031020408163265232 +/- 0.0020260691666923584</t>
+          <t>0.007224489795918432 +/- 0.001991652718164207</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-0.008897959183673487 +/- 0.002593041661105078</t>
+          <t>-0.01510204081632648 +/- 0.002205592830384705</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.009061224489795915 +/- 0.0034090796763789565</t>
+          <t>0.008897959183673509 +/- 0.002226641909711958</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-0.002612244897959215 +/- 0.0014396075174325396</t>
+          <t>-0.00538775510204077 +/- 0.0016509182380536266</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>-0.0020408163265306367 +/- 0.00031616190581285416</t>
+          <t>0.0013877551020408329 +/- 0.0003265306122449019</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.004367346938775496 +/- 0.002345074681179288</t>
+          <t>-8.163265306116995e-05 +/- 0.0018143763894606167</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>-0.0028571428571428914 +/- 0.0012514048748372307</t>
+          <t>0.0073877551020409046 +/- 0.0008839350133758357</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.001224489795918371 +/- 0.00111032412316207</t>
+          <t>0.0027755102040816658 +/- 0.0004396052903783321</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.016734693877551 +/- 0.0022206482463241807</t>
+          <t>0.024163265306122516 +/- 0.0013137532195454102</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.003591836734693843 +/- 0.001599666770797156</t>
+          <t>0.0017142857142857459 +/- 0.0016407960197748416</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.019836734693877523 +/- 0.002739259058867342</t>
+          <t>0.014653061224489861 +/- 0.0013093073414159702</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.0007346938775510293 +/- 0.000541489761690684</t>
+          <t>-8.163265306120327e-05 +/- 0.00016326530612240653</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.0018775510204081525 +/- 0.0010829795233813211</t>
+          <t>3.3306690738754695e-17 +/- 0.00040816326530608294</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.00020408163265306367 +/- 0.0006644416569836695</t>
+          <t>-0.0002448979591836209 +/- 0.0006631868085416712</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.00020408163265306367 +/- 0.00020408163265306367</t>
+          <t>0.00016326530612245093 +/- 0.00019995834634964956</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-0.0020408163265306367 +/- 0.00048294528841630097</t>
+          <t>0.0021224489795918624 +/- 0.0005097957549713039</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.011020408163265305 +/- 0.001471653581822017</t>
+          <t>0.01616326530612252 +/- 0.0018543374190368232</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>-0.0024081632653061512 +/- 0.0003850604543696619</t>
+          <t>-8.163265306120327e-05 +/- 0.00016326530612240653</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.005224489795918319 +/- 0.001061224489795931</t>
+          <t>0.002326530612244926 +/- 0.000708136798893783</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.006448979591836712 +/- 0.00244080267554712</t>
+          <t>0.00734693877551027 +/- 0.0013537244042266833</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.006326530612244874 +/- 0.0026087348867387464</t>
+          <t>0.009265306122449024 +/- 0.0015707658289709004</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.0014285714285714346 +/- 0.0010682654961879407</t>
+          <t>0.0006122448979592021 +/- 0.0008610213514175016</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.009061224489795905 +/- 0.001739369449196938</t>
+          <t>0.007836734693877623 +/- 0.0014233139407479585</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.0071428571428571175 +/- 0.0017340935335712862</t>
+          <t>0.010938775510204113 +/- 0.0019472425211227071</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>-0.004408163265306164 +/- 0.0012487394727165966</t>
+          <t>0.0042040816326531115 +/- 0.0018258178976608415</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.0023157894736842597 +/- 0.0009698438569182726</t>
+          <t>-0.001333333333333331 +/- 0.000812339431774744</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.005614035087719238 +/- 0.0014968932636983522</t>
+          <t>-0.00228070175438595 +/- 0.0018846384564204582</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.002421052631578979 +/- 0.0011996716489318536</t>
+          <t>-0.0052982456140350685 +/- 0.001484090244389914</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.005929824561403474 +/- 0.0019054279273523433</t>
+          <t>-0.0018245614035087621 +/- 0.0020387142521170534</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.001017543859649106 +/- 0.0010461790537456374</t>
+          <t>0.0032280701754386133 +/- 0.0008273562191264495</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.0036140350877192696 +/- 0.001789473684210525</t>
+          <t>0.005368421052631589 +/- 0.0016311072700588927</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.00024561403508772673 +/- 0.00027404384827744695</t>
+          <t>-0.0002456140350877045 +/- 0.0002246710258748233</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0031929824561403807 +/- 0.0012982456140350756</t>
+          <t>0.007859649122807044 +/- 0.0019102677317636846</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.014175438596491263 +/- 0.0031547742867353095</t>
+          <t>0.017298245614035125 +/- 0.002436260398152968</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.023087719298245636 +/- 0.003094092306673471</t>
+          <t>0.024771929824561435 +/- 0.0034848306015256513</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.000526315789473708 +/- 0.0008340255665968348</t>
+          <t>-0.0017894736842105185 +/- 0.002136896839099668</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-0.002175438596491208 +/- 0.0011402159164401275</t>
+          <t>-0.0008421052631578663 +/- 0.0012474658831320318</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-0.0006315789473684052 +/- 0.0014192104151688856</t>
+          <t>-0.0029122807017543883 +/- 0.0016083040893145068</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.0003508771929824794 +/- 0.002279351827215653</t>
+          <t>0.014140350877192986 +/- 0.0032313103494295585</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.006982456140350879 +/- 0.0012300735538918013</t>
+          <t>0.0064561403508772265 +/- 0.0025602015925550448</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.0020350877192982673 +/- 0.0016367584266232405</t>
+          <t>0.002701754385964916 +/- 0.0008457523363644805</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-0.0011929824561403457 +/- 0.0012767302034147497</t>
+          <t>0.00470175438596494 +/- 0.0011867743526517796</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.007824561403508757 +/- 0.0022469842310996876</t>
+          <t>-0.005578947368421028 +/- 0.0025030606072999045</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.0035087719298245944 +/- 0.0013858538707460794</t>
+          <t>0.003614035087719325 +/- 0.0008601860120793957</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3.5087719298254604e-05 +/- 0.00029146048641818595</t>
+          <t>3.5087719298243504e-05 +/- 0.00018895315112751508</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.01347368421052635 +/- 0.0023179150266545616</t>
+          <t>-0.00045614035087717666 +/- 0.002466394634496847</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.0003859649122807451 +/- 0.0012300735538917937</t>
+          <t>-0.004736842105263173 +/- 0.0006325528553445676</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.0010877192982456374 +/- 0.0008369726625878354</t>
+          <t>-0.0008421052631578773 +/- 0.001133718906765155</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.508771929826571e-05 +/- 0.001508771929824576</t>
+          <t>-0.0001403508771929629 +/- 0.0010193571260585128</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.0015789473684210908 +/- 0.0012280701754386017</t>
+          <t>0.0020000000000000018 +/- 0.0012058133528027933</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.0007017543859648811 +/- 0.0004151634935508441</t>
+          <t>0.0009473684210526412 +/- 0.0006848849577523995</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.0028771929824561782 +/- 0.0013751521362993337</t>
+          <t>0.000982456140350907 +/- 0.0012533734104906503</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0.0029473684210526542 +/- 0.0009441139682157031</t>
+          <t>-0.003157894736842104 +/- 0.0014295823710500535</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-0.002175438596491208 +/- 0.0005614035087718961</t>
+          <t>-0.001754385964912264 +/- 0.001331485330597226</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.005614035087719282 +/- 0.000954489158507746</t>
+          <t>-0.0032631578947368233 +/- 0.001782580462579714</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-0.0009122807017543644 +/- 0.000548087696554864</t>
+          <t>-0.0008421052631578773 +/- 0.0004493420517496881</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.0003157894736841915 +/- 0.0005536748715108686</t>
+          <t>-0.0012631578947368215 +/- 0.0008479330507785614</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,122 +2826,122 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.0015789473684210352 +/- 0.0014144311839120057</t>
+          <t>-0.010245614035087702 +/- 0.0008848786114328903</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.005543859649122784 +/- 0.001427858943815838</t>
+          <t>-0.005999999999999972 +/- 0.0017078025998088179</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>-0.000210526315789461 +/- 0.0004493420517496466</t>
+          <t>-0.000491228070175409 +/- 0.0003907203061634868</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.0006666666666666377 +/- 0.0003985198839158052</t>
+          <t>0.002421052631578979 +/- 0.0007598739588669409</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.0024210526315789904 +/- 0.0011578947368421186</t>
+          <t>0.004491228070175446 +/- 0.0014869908842397902</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>-0.0008421052631578773 +/- 0.0008764909471436212</t>
+          <t>-0.005192982456140327 +/- 0.001348026155249021</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-0.0003157894736841915 +/- 0.0003310168818265276</t>
+          <t>-0.001087719298245604 +/- 0.0011364305081194089</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.000982456140350907 +/- 0.0004912280701754456</t>
+          <t>7.017543859649811e-05 +/- 0.0014786882460144169</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.005228070175438559 +/- 0.0011789682537832725</t>
+          <t>-0.00031578947368418044 +/- 0.0016933232999317286</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-0.0014736842105262827 +/- 0.002373548705303542</t>
+          <t>-0.0034035087719297974 +/- 0.001782580462579737</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.006912280701754392 +/- 0.0009679378402901056</t>
+          <t>-0.009543859649122789 +/- 0.001348026155249035</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>-0.005403508771929777 +/- 0.0017973682069986968</t>
+          <t>0.00024561403508773785 +/- 0.001455611825452033</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.002877192982456167 +/- 0.0007156518615568738</t>
+          <t>0.00045614035087723217 +/- 0.0008457523363644838</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-3.50877192982102e-05 +/- 0.0008938764352882232</t>
+          <t>-0.0025263157894736764 +/- 0.0007814406123270155</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-0.0008771929824561098 +/- 0.0003595421321389441</t>
+          <t>-0.000210526315789461 +/- 0.00059130875601238</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>0.0006315789473684164 +/- 0.0012134467695291728</t>
+          <t>0.00010526315789476382 +/- 0.0012655921962716836</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>-0.010070175438596462 +/- 0.0016610246145325695</t>
+          <t>-0.016245614035087695 +/- 0.0025881801552154506</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-0.0011929824561403347 +/- 0.0007393441230072127</t>
+          <t>-0.0005964912280701617 +/- 0.0017121225121060964</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-0.0073333333333332916 +/- 0.0015087719298245573</t>
+          <t>-0.0005263157894736748 +/- 0.0023393274808117016</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>0.000526315789473708 +/- 0.0004225120904839655</t>
+          <t>0.0006315789473684497 +/- 0.0004912280701754582</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>-0.0013684210526315633 +/- 0.0004823763889427362</t>
+          <t>-0.0012982456140350652 +/- 0.0007199398080239743</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.00042105263157895536 +/- 0.00021052631578950544</t>
+          <t>-0.000421052631578922 +/- 0.00046549119864634385</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-0.0036491228070175017 +/- 0.0008764909471436293</t>
+          <t>0.00024561403508772673 +/- 0.0018099958423198326</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.01750877192982453 +/- 0.00235610834585257</t>
+          <t>-0.016736842105263126 +/- 0.0018099958423198473</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2951,107 +2951,107 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.00038436670702116636</t>
+          <t>-0.00045614035087716555 +/- 0.00031578947368419156</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-0.003964912280701727 +/- 0.0008457523363644889</t>
+          <t>0.0013684210526316077 +/- 0.0009730122543060901</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-0.0029473684210526096 +/- 0.00154704615333675</t>
+          <t>0.00014035087719300733 +/- 0.002135456007677615</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>-0.0007368421052631136 +/- 0.0003310168818265276</t>
+          <t>-0.0014736842105263158 +/- 0.0003779063022550652</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.00010526315789476382 +/- 0.001284900591129853</t>
+          <t>-0.000491228070175409 +/- 0.0010894157681585969</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-0.004245614035087708 +/- 0.001389845776865861</t>
+          <t>0.0014035087719298622 +/- 0.0018028396601635327</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>0.00010526315789475272 +/- 0.0014640453364929932</t>
+          <t>-0.0002456140350877156 +/- 0.0017756604812463209</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-0.00796491228070173 +/- 0.0017547368070245546</t>
+          <t>-0.007263157894736816 +/- 0.0006286481707778629</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>0.0001052631578947416 +/- 0.0002740438482774341</t>
+          <t>-0.0001754385964912175 +/- 0.00023537557657891107</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>-0.00045614035087717666 +/- 0.0010532162119160503</t>
+          <t>-0.0014385964912280503 +/- 0.001450528183059239</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>-7.017543859648701e-05 +/- 0.001375152136299336</t>
+          <t>-0.006245614035087698 +/- 0.0019396877138365353</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-0.0024561403508771675 +/- 0.0007190842642778396</t>
+          <t>-0.0001052631578947305 +/- 0.0004166435820013054</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.005438596491228087 +/- 0.0011872929344342693</t>
+          <t>-0.0013684210526315743 +/- 0.0014248379301225885</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>0.00014035087719302953 +/- 0.0008031946064743578</t>
+          <t>-0.0029122807017543774 +/- 0.0008601860120793872</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>-0.003438596491228052 +/- 0.0010023057443568986</t>
+          <t>-0.0034035087719298195 +/- 0.001480768269895373</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>0.0001754385964912175 +/- 0.0001754385964912175</t>
+          <t>0.00042105263157895536 +/- 0.0003058876451607739</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>-0.0001754385964912175 +/- 0.00039229262763151846</t>
+          <t>-0.0014385964912280614 +/- 0.000726747900954688</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>-0.0002456140350877045 +/- 0.0004166435820013054</t>
+          <t>-0.003087719298245595 +/- 0.0006982367979695605</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>3.5087719298243504e-05 +/- 0.0001052631578947305</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-0.000210526315789461 +/- 0.0003907203061634868</t>
+          <t>-0.0002456140350876934 +/- 0.0006848849577524047</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>-0.0014035087719298067 +/- 0.0010169387190308225</t>
+          <t>0.0007017543859649366 +/- 0.001754385964912295</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3061,37 +3061,37 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0002219142217661887</t>
+          <t>-0.0007719298245613682 +/- 0.0007492686492653351</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>-0.0012631578947368328 +/- 0.0012375573395472488</t>
+          <t>7.017543859650921e-05 +/- 0.0013751521362993235</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>-0.004140350877192967 +/- 0.0015116252090202217</t>
+          <t>-0.005473684210526297 +/- 0.001089415768158569</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>-0.0006666666666666488 +/- 0.0006364335841129033</t>
+          <t>0.0017192982456140427 +/- 0.0006740130776244699</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>0.0011929824561403902 +/- 0.0011971033059110093</t>
+          <t>7.017543859650921e-05 +/- 0.001329634759403267</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>0.0034385964912280963 +/- 0.0015278274426019068</t>
+          <t>0.0059298245614035185 +/- 0.001580506053270918</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>-0.005368421052631545 +/- 0.0010648414670521792</t>
+          <t>0.00045614035087720994 +/- 0.000845752336364505</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.00030441400304416223 +/- 0.0007378508154362804</t>
+          <t>0.001902587519025878 +/- 0.00146388006557621</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,157 +3111,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.0033105022831049656 +/- 0.0013934424218873906</t>
+          <t>0.00844748858447487 +/- 0.0017586331823883094</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.005707762557077678 +/- 0.0012388752356240272</t>
+          <t>0.0032343987823439833 +/- 0.0014364220767257875</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7.610350076098227e-05 +/- 0.0014419555039190631</t>
+          <t>0.00878995433789954 +/- 0.0017055505959676412</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.006430745814307415 +/- 0.0018442345229912678</t>
+          <t>0.0022450532724505256 +/- 0.00128983647311097</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.0040334855403349025 +/- 0.0016777327005364302</t>
+          <t>0.012633181126331805 +/- 0.002124092197405305</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.00011415525114152336 +/- 0.00045183950102881826</t>
+          <t>0.0006088280060883022 +/- 0.00042372635942391357</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.0009512937595128723 +/- 0.0012533994742770526</t>
+          <t>-0.004071537290715377 +/- 0.0010634085702041181</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.0646499238964992 +/- 0.0037261582755736956</t>
+          <t>0.029680365296803644 +/- 0.0014932585137251537</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.06240487062404865 +/- 0.0031608157773660803</t>
+          <t>0.07157534246575344 +/- 0.003889663250548127</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.0019025875190258224 +/- 0.0018406981160498906</t>
+          <t>0.001522070015220689 +/- 0.0016498845805691536</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.001712328767123239 +/- 0.0014761921416492393</t>
+          <t>0.006012176560121751 +/- 0.0019684196585049545</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-0.0009893455098935132 +/- 0.0015522129417329567</t>
+          <t>0.005175038051750358 +/- 0.0013420998545318349</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.003957382039573754 +/- 0.002258877028866954</t>
+          <t>0.004984779299847775 +/- 0.002682311042401381</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.008523592085235865 +/- 0.0014854810727506253</t>
+          <t>0.011149162861491613 +/- 0.0024008815151213567</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.0015220700152206556 +/- 0.0007981802497489817</t>
+          <t>-0.001255707762557079 +/- 0.0014037950339190872</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.004642313546423171 +/- 0.0011641597062997011</t>
+          <t>-0.0017123287671232945 +/- 0.0015053303230481425</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0014459665144596068 +/- 0.001975761793873243</t>
+          <t>0.006164383561643849 +/- 0.0023993733288332477</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-0.0024733637747336944 +/- 0.001276294507705368</t>
+          <t>0.0038432267884322747 +/- 0.0018598705342237395</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-3.8051750380552195e-05 +/- 0.0003972719371731358</t>
+          <t>0.00045662100456621556 +/- 0.0005327245053272422</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.008257229832572276 +/- 0.003183865242885676</t>
+          <t>0.0020547945205479424 +/- 0.0020434888252812205</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-0.011491628614916326 +/- 0.0013592519862626739</t>
+          <t>-0.005631659056316596 +/- 0.001126228963999152</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-0.0007229832572298811 +/- 0.0012087047316795068</t>
+          <t>0.0022831050228310336 +/- 0.0007417651708378249</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>-0.0007229832572298922 +/- 0.000954333044443253</t>
+          <t>0.002168949771689477 +/- 0.0013830123170004715</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.0007610350076103 +/- 0.001006754684575562</t>
+          <t>0.00300608828006087 +/- 0.0010823030938605857</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.00011415525114151226 +/- 0.0005119339439525473</t>
+          <t>-0.001255707762557079 +/- 0.0009783074682026102</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.0023972602739725677 +/- 0.0019480861090061172</t>
+          <t>0.008751902587519012 +/- 0.0016322382488224592</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-0.006506849315068541 +/- 0.0013447942958198164</t>
+          <t>-0.0011796042617960522 +/- 0.0013447942958197962</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-0.016476407914764124 +/- 0.002077569816547758</t>
+          <t>-0.003691019786910199 +/- 0.00109030051612592</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.006925418569254227 +/- 0.001248190218177827</t>
+          <t>-0.004375951293759528 +/- 0.0012182504256911823</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-0.0009893455098935022 +/- 0.000854259677345662</t>
+          <t>0.0012937595129375867 +/- 0.0005161590550323341</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.0004566210045662489 +/- 0.0007179589902630599</t>
+          <t>0.0014079147640791323 +/- 0.0007619857075532869</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,122 +3271,122 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.0016362252663623012 +/- 0.0017190802127970437</t>
+          <t>-0.006773211567732129 +/- 0.0016829029214228226</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.007420091324200961 +/- 0.0011447190986675036</t>
+          <t>-0.002587519025875207 +/- 0.0016393195759922354</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>-0.0005707762557078056 +/- 0.0005956041035958206</t>
+          <t>-0.0004946727549467456 +/- 0.0005119339439525951</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>7.610350076099337e-05 +/- 0.0009596286311201144</t>
+          <t>0.0027016742770167414 +/- 0.0007881398469257289</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.00026636225266368774 +/- 0.0012277219029605488</t>
+          <t>0.0019786910197868933 +/- 0.0008972470412900737</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-0.009741248097412513 +/- 0.001834394336863609</t>
+          <t>-0.017009132420091323 +/- 0.0019029679984855395</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-0.0006088280060883245 +/- 0.0007456589780161859</t>
+          <t>0.00011415525114155667 +/- 0.0008685473523983062</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.0011415525114155777 +/- 0.000833672081438619</t>
+          <t>0.002473363774733628 +/- 0.0010796241216979674</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.007800608828006162 +/- 0.0015149185112172294</t>
+          <t>-0.0073059360730593605 +/- 0.0016215582764583462</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.0004185692541856745 +/- 0.0012671861343490686</t>
+          <t>0.0005327245053272534 +/- 0.0007259811274101678</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.0036910197869101436 +/- 0.0011672649657669672</t>
+          <t>0.004642313546423127 +/- 0.0014419555039190607</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>-0.027891933028919368 +/- 0.0021729515274382417</t>
+          <t>-0.021194824961948244 +/- 0.0026365771995920636</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-0.008751902587519044 +/- 0.0012033020015861395</t>
+          <t>-0.001217656012176571 +/- 0.0011516549429544602</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.00445205479452061 +/- 0.001007473538422675</t>
+          <t>0.0020928462709284613 +/- 0.001264898792891531</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-0.0005707762557077944 +/- 0.0004582037510955908</t>
+          <t>0.00011415525114155667 +/- 0.0005119339439525951</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>-0.0015981735159817934 +/- 0.002338248325074178</t>
+          <t>0.00041856925418568556 +/- 0.0014976155748976157</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>-0.0025875190258752402 +/- 0.0015945454215948879</t>
+          <t>-0.0018264840182648401 +/- 0.0013485574693051085</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-0.006050228310502326 +/- 0.0016798888930474943</t>
+          <t>-0.0060882800608828 +/- 0.001250508122157915</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-0.007648401826484075 +/- 0.002798550381765113</t>
+          <t>-0.010121765601217659 +/- 0.001533443050198613</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>0.000380517503805089 +/- 0.0002947475910355541</t>
+          <t>0.0014840182648401701 +/- 0.0006688887302605147</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3.805175038046338e-05 +/- 0.0006468797564687721</t>
+          <t>0.0017123287671232835 +/- 0.0008205425666989115</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>-0.0005327245053272977 +/- 0.000663454938134023</t>
+          <t>0.00011415525114155667 +/- 0.00041856925418570784</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-0.0070395738203957725 +/- 0.00203674637611455</t>
+          <t>-0.005136986301369872 +/- 0.0019643697867793536</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.00471841704718422 +/- 0.002106294140501973</t>
+          <t>-0.0014840182648401922 +/- 0.0017308318745120445</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3396,107 +3396,107 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>0.0002283105022830467 +/- 0.001009627029027504</t>
+          <t>-0.00022831050228311334 +/- 0.000388053235433255</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-0.007800608828006139 +/- 0.001919634437690937</t>
+          <t>-0.0031202435312024266 +/- 0.0012365355258197753</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-0.009132420091324246 +/- 0.0017520341603076775</t>
+          <t>0.004490106544901051 +/- 0.002110414706828326</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.0009132420091323646 +/- 0.0006634549381340383</t>
+          <t>0.003462709284627108 +/- 0.0005231250793328776</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-0.011035007610350145 +/- 0.002308333468508845</t>
+          <t>0.0025875190258751847 +/- 0.0017337573439717613</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-0.0016362252663622901 +/- 0.0022450532724505364</t>
+          <t>-0.0091324200913242 +/- 0.0018009375291018642</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-0.009589041095890437 +/- 0.0006546670675070525</t>
+          <t>-0.0011415525114155222 +/- 0.0015220700152206862</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-0.004185692541856967 +/- 0.0015781157803141327</t>
+          <t>-0.008789954337899553 +/- 0.0019950877821793608</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>-0.00019025875190261665 +/- 0.00045820375109558624</t>
+          <t>7.610350076103778e-05 +/- 0.00015220700152207556</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-0.015753424657534286 +/- 0.0021538769707891772</t>
+          <t>-0.005707762557077644 +/- 0.001089636306185412</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>-0.007838660578386659 +/- 0.0012176560121765754</t>
+          <t>-0.006773211567732107 +/- 0.0017085193546912988</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.001369863013698569 +/- 0.001156673071047972</t>
+          <t>-0.0011415525114155222 +/- 0.001191208207191666</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-0.01076864535768649 +/- 0.001329635099669433</t>
+          <t>-0.011529680365296802 +/- 0.001676437653874483</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>-0.00350076103500766 +/- 0.0009893455098934501</t>
+          <t>-0.0047184170471841645 +/- 0.0014459665144596692</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>-0.020738203957382084 +/- 0.0022073295300263545</t>
+          <t>-0.007229832572298334 +/- 0.0017437502644428572</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>7.610350076100447e-05 +/- 0.0003317274690669911</t>
+          <t>-0.0003044140030441511 +/- 0.0005845620812685607</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>-0.0019406392694064523 +/- 0.0007309502554147186</t>
+          <t>0.0009132420091324201 +/- 0.0008542596773456364</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>0.0008371385083713045 +/- 0.0002847532257818933</t>
+          <t>0.00045662100456620445 +/- 0.0010462501586657284</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>0.000380517503805089 +/- 0.00017017260102736265</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>-0.0037290715372907735 +/- 0.0009746003405529441</t>
+          <t>0.0008371385083713823 +/- 0.0011002155475495136</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>-0.008599695585996991 +/- 0.0009951824072010566</t>
+          <t>-0.0005707762557077501 +/- 0.0014761921416492347</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3506,37 +3506,37 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>-3.80517503805633e-05 +/- 0.0006004464930768224</t>
+          <t>0.0013318112633181056 +/- 0.0008205425666989089</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>-0.006963470319634757 +/- 0.001296554416849361</t>
+          <t>-0.0039573820395738205 +/- 0.0014757016308725361</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>-0.004756468797564739 +/- 0.0012875893695349257</t>
+          <t>-0.00186453576864537 +/- 0.0013871937696771865</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>-0.0008371385083714266 +/- 0.0007761064708664925</t>
+          <t>-0.00019025875190260556 +/- 0.0009359493056506107</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>-0.00171232876712335 +/- 0.0007466292568626064</t>
+          <t>0.0003044140030441511 +/- 0.00164812844959726</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>-0.007343987823439935 +/- 0.0014242745260435975</t>
+          <t>-0.010540334855403366 +/- 0.0015034053474230077</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>-0.0025875190258752402 +/- 0.0007572202717706232</t>
+          <t>0.0023972602739725903 +/- 0.0011294385144334901</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0007301935012778759 +/- 0.0017661024640303522</t>
+          <t>-0.0006206644760860969 +/- 0.0012223927742083308</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.000620664476086119 +/- 0.0031067566848491874</t>
+          <t>-0.0010952902519167028 +/- 0.0024762066385999523</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0008762322015334334 +/- 0.0017524644030668043</t>
+          <t>-0.007228915662650548 +/- 0.001393120410977651</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.0009492515516611455 +/- 0.0012348692607000997</t>
+          <t>-0.0015334063526834195 +/- 0.0014767249664955507</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.003577948156261379 +/- 0.0015123997938815508</t>
+          <t>0.0009492515516612343 +/- 0.0013483888508666962</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.00036509675063887135 +/- 0.0016245779818391403</t>
+          <t>0.00514786418400881 +/- 0.002334621727455028</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.00032858707557500424 +/- 0.00019661061727397315</t>
+          <t>-0.0002555677254472144 +/- 0.0003669176933596457</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.00784958013873679 +/- 0.001157420042654056</t>
+          <t>-0.0013508579773639396 +/- 0.0009938413719471433</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.016100766703176374 +/- 0.003091272268820665</t>
+          <t>0.011683096020445472 +/- 0.002682902237440512</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.015991237677984695 +/- 0.003988755102956614</t>
+          <t>0.01004016064257034 +/- 0.001683012861864349</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-0.003249361080686364 +/- 0.0018505039645818461</t>
+          <t>-3.650967506384495e-05 +/- 0.000900983036090021</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.0053669222343920905 +/- 0.0016249881770184571</t>
+          <t>-0.010624315443592514 +/- 0.0016445572295809032</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.005001825483753231 +/- 0.0018258488134428508</t>
+          <t>0.006754289886820064 +/- 0.0016429353778751271</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-0.03680175246440304 +/- 0.0036061506315781602</t>
+          <t>-0.02037239868565165 +/- 0.005377715265285712</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-0.015005476451259558 +/- 0.0023910353165436803</t>
+          <t>-0.02402336619204084 +/- 0.004275842562090481</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>-0.002336619204089063 +/- 0.0015762711314291867</t>
+          <t>-0.0014603870025556298 +/- 0.0014512308809311201</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-0.003395399780941932 +/- 0.0012652591055979355</t>
+          <t>-0.004965315808689241 +/- 0.002233962547028609</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-0.0021540708287695943 +/- 0.0017467504510997787</t>
+          <t>0.0006936838262139977 +/- 0.0022532711389864047</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-0.006389193136181059 +/- 0.0013974194384085373</t>
+          <t>-0.004928806133625374 +/- 0.0014163683637291383</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-0.0005476451259583404 +/- 0.00033660257237284544</t>
+          <t>3.650967506392266e-05 +/- 0.00044565737917977413</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.01861993428258486 +/- 0.0015745789450783444</t>
+          <t>-0.02322015334063522 +/- 0.0029262453318019393</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.004271631982475388 +/- 0.002203019326987307</t>
+          <t>0.0015699160277473866 +/- 0.001155114422749647</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-0.00901788974078127 +/- 0.0014332082093019573</t>
+          <t>-0.005805038335158763 +/- 0.0009991918352247981</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.0048557867834975845 +/- 0.0015579838111246546</t>
+          <t>-0.0018985031033223354 +/- 0.0012731358725200823</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.012705366922234363 +/- 0.0015558434284529102</t>
+          <t>-0.007374954362906116 +/- 0.0016064257028112466</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.0011317999269806812 +/- 0.00041467019684555484</t>
+          <t>0.00040160642570286065 +/- 0.0004746257758305984</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>-0.013618108798831663 +/- 0.0013067199830721545</t>
+          <t>-0.012960934647681577 +/- 0.0037774724321781297</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-0.0035779481562614015 +/- 0.001703089271951902</t>
+          <t>0.011792625045637151 +/- 0.0018476204350317705</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>-0.000985761226725046 +/- 0.0023720052385222136</t>
+          <t>0.006316173786053347 +/- 0.0017964095801595668</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.003139832055494729 +/- 0.0015334063526834688</t>
+          <t>0.002154070828769672 +/- 0.0014825805406533132</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.00131434830230015 +/- 0.0006365679362600393</t>
+          <t>4.4408920985006264e-17 +/- 0.0004319883010660709</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.0011683096020445594 +/- 0.00045600569539235833</t>
+          <t>3.3306690738754695e-17 +/- 0.0007830452935205126</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,272 +3716,272 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.004636728733114315 +/- 0.0017283388650667743</t>
+          <t>0.0015699160277473979 +/- 0.001356765547722702</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.0010952902519168028 +/- 0.002360457082912677</t>
+          <t>0.007484483388097906 +/- 0.0022162906477950096</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0.0007667031763417653 +/- 0.0008397225264695141</t>
+          <t>-0.0017524644030667447 +/- 0.0005841548010222783</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.00018254837531943567 +/- 0.0007347430375136226</t>
+          <t>0.001022270901789013 +/- 0.000273213390783036</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.00828769623950345 +/- 0.0013168812557043707</t>
+          <t>-0.008324205914567307 +/- 0.0016392803446983308</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>0.004527199707922635 +/- 0.0013582384255376439</t>
+          <t>0.004746257758305994 +/- 0.001306209844468653</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>0.00014603870025561294 +/- 0.0009407885160076788</t>
+          <t>-0.0003285870755749931 +/- 0.0009301014386898042</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.009163928441036839 +/- 0.001482580540653304</t>
+          <t>-0.005878057685286553 +/- 0.0019418891780901334</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.002884264330047481 +/- 0.0017391026453179186</t>
+          <t>0.006717780211756163 +/- 0.0014893083646857366</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-0.001277838627236194 +/- 0.0024010490029145446</t>
+          <t>-0.0006936838262138978 +/- 0.0015093119100835634</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.00021905805038338055 +/- 0.0020275200258364065</t>
+          <t>0.0016064257028112982 +/- 0.0012668383769914152</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.01332603139832057 +/- 0.002743089267070006</t>
+          <t>0.0005841548010223407 +/- 0.0028383777620411693</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0005841548010222964 +/- 0.0016666976576142063</t>
+          <t>-0.0012413289521722604 +/- 0.0008972767964545058</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.005805038335158841 +/- 0.0008236958139962334</t>
+          <t>0.0008397225264695663 +/- 0.001166596955726212</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-0.00010952902519163476 +/- 0.0007838959676372472</t>
+          <t>-0.0001825483753194246 +/- 0.000468975267567184</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>-0.0020810514786418154 +/- 0.0016893370282963663</t>
+          <t>-0.00047462577583053946 +/- 0.0011665969557262037</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0008762322015334445 +/- 0.0013183986918778876</t>
+          <t>-0.005914567360350431 +/- 0.0012520210441388923</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0.0061336254107338785 +/- 0.0015981065080860907</t>
+          <t>0.00617013508579779 +/- 0.0009156579922588173</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.005366922234392136 +/- 0.0009243511428384242</t>
+          <t>0.0031763417305586627 +/- 0.002072064786223115</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>0.0031033223804308395 +/- 0.0008040421885923821</t>
+          <t>-0.0016429353778750987 +/- 0.0008040421885923896</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>-0.0010222709017889242 +/- 0.0007265333604283305</t>
+          <t>-0.0018985031033223131 +/- 0.0005841548010222769</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.0001825483753194801 +/- 0.0002943504106717525</t>
+          <t>-3.6509675063889356e-05 +/- 0.00010952902519166809</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.008470244614822963 +/- 0.0008913147583595246</t>
+          <t>-0.0024826579043445984 +/- 0.0010170418603274282</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.010843373493975872 +/- 0.0016413119235479388</t>
+          <t>0.010660825118656491 +/- 0.001944290172427057</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>0.0003650967506390046 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>7.301935012783422e-05 +/- 0.0006692333983141072</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>-0.003504928806133567 +/- 0.0010606673272240974</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>-0.00226359985396124 +/- 0.0016147020363268506</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>-0.0002555677254471811 +/- 0.000817197126162797</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>-3.650967506384495e-05 +/- 0.0010384419608125421</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>0.01000365096750645 +/- 0.0015420746317592383</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-0.0019350127783862026 +/- 0.0012964790729875586</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>0.0020080321285141033 +/- 0.0011341529439218014</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>-0.00014603870025555742 +/- 0.00017886014916268752</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>0.0009492515516612455 +/- 0.0008032128514056183</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>0.003212851405622552 +/- 0.0011288517585790838</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>-0.0017889740781306563 +/- 0.0006622255256377109</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>0.0030668127053669727 +/- 0.001947030540485335</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>0.005220883534136589 +/- 0.0016893370282963507</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>0.011171960569550976 +/- 0.0019263827613395959</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>-0.00014603870025554634 +/- 0.00024217778680945504</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>0.0006206644760861968 +/- 0.0008007196859971369</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>0.0012413289521723825 +/- 0.0005702993556704395</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>0.0009857612267251015 +/- 0.0007311056734027199</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>-0.006973347937203334 +/- 0.0015004543693343817</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>-0.0028842643300474257 +/- 0.0011937044705565558</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>-0.000401606425702794 +/- 0.0004456573791797577</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>-0.008616283315078466 +/- 0.0010731608949762187</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>0.0008762322015334556 +/- 0.001298020360323564</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>0.004381161007667045 +/- 0.0016570727590960476</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>0.004381161007667067 +/- 0.0009090835778013021</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>-0.00014603870025554634 +/- 0.00033461669915704637</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>0.008835341365461857 +/- 0.00111698127351429</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>-0.0001825483753194246 +/- 0.0013782100100895825</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>-0.00043811610076663896 +/- 0.0005841548010222756</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>0.019204089083607177 +/- 0.0019263827613395866</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>0.0014968966776195969 +/- 0.0013409541929322306</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>0.00803212851405627 +/- 0.0018472596773528138</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>7.301935012782312e-05 +/- 0.0003577202983254226</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>0.001204819277108471 +/- 0.0006936838262139194</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>0.0020445418035779928 +/- 0.0010352279575580668</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>0.0015334063526835084 +/- 0.0008293403936911741</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>-0.002154070828769572 +/- 0.0011711584470496888</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>0.0032493610806864194 +/- 0.000598803193386519</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>0.0031033223804308395 +/- 0.001358729030005745</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>0.0005111354508945398 +/- 0.0003346166991570632</t>
-        </is>
-      </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.0015699160277473866 +/- 0.0006741944254333427</t>
+          <t>3.650967506393377e-05 +/- 0.0004146701968455998</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.0010587805768528802 +/- 0.0017467504510997756</t>
+          <t>-0.0024826579043446205 +/- 0.0012086853126868794</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.004417670682730956 +/- 0.001754364918106446</t>
+          <t>0.004162102957283731 +/- 0.0012456168024265796</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>-0.001460387002555652 +/- 0.000863976602132095</t>
+          <t>0.00040160642570286065 +/- 0.00077362614459353</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>0.0064622124863088935 +/- 0.0023663790322159583</t>
+          <t>0.005878057685286642 +/- 0.0011127966888739168</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>-0.0023731288791529414 +/- 0.0016510287045775937</t>
+          <t>0.01161007667031767 +/- 0.0015035604441017891</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>-0.000620664476086108 +/- 0.0013762743209179142</t>
+          <t>-0.0015334063526834085 +/- 0.0006692333983141072</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.00560061799922752 +/- 0.0015377388364151818</t>
+          <t>-0.0044032444959443365 +/- 0.0013840457989315327</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,157 +4001,157 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.0010428736964078866 +/- 0.0020442052719040994</t>
+          <t>0.004094244882193942 +/- 0.002226888421073729</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.00316724604094244 +/- 0.002071392456978295</t>
+          <t>-0.00540749324063341 +/- 0.002143597825494261</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3.862495171879088e-05 +/- 0.00235865347868242</t>
+          <t>-0.0006952491309385467 +/- 0.001725632128519766</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.008497489378138313 +/- 0.0018763936348383252</t>
+          <t>-0.0080339899575125 +/- 0.001945102867827594</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.003283120896098868 +/- 0.002117337979708879</t>
+          <t>-0.0065276168404789 +/- 0.0023268127434266576</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.000463499420625757 +/- 0.0002890426718249676</t>
+          <t>0.0008497489378138878 +/- 0.00015449980687525235</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.0019698725376593672 +/- 0.0018560083084950088</t>
+          <t>-0.0016608729239088182 +/- 0.0012581303572732517</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-0.013711857860177711 +/- 0.0032188747238317034</t>
+          <t>-0.024063344920818807 +/- 0.0027962437694458503</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.020587099266125942 +/- 0.0039011201235998527</t>
+          <t>-0.03310158362302044 +/- 0.002681862547213575</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0019698725376593117 +/- 0.0011645278819375445</t>
+          <t>0.004789494013132533 +/- 0.0012716939075438079</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-0.012475859405175782 +/- 0.0025797882548468953</t>
+          <t>-0.010158362302047075 +/- 0.002065983641609309</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.00482811896485128 +/- 0.0018624277251820943</t>
+          <t>0.004055619930475129 +/- 0.0020088688488135793</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-0.006759366550791834 +/- 0.002775895497695001</t>
+          <t>-0.009347238315952045 +/- 0.003453856918672558</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.01927385090768634 +/- 0.0026729471265810917</t>
+          <t>0.020896098879876458 +/- 0.002017760971279879</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>-0.001429123213595973 +/- 0.0015260522414166416</t>
+          <t>-0.0037852452684433713 +/- 0.0009586460908451691</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-0.007493240633449217 +/- 0.0020814513071158725</t>
+          <t>-0.004364619544225535 +/- 0.0016572760102684528</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.006334492081884868 +/- 0.001754780485376673</t>
+          <t>0.002896871378910837 +/- 0.0009809521127230835</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>-0.009192738509076903 +/- 0.001483922187122324</t>
+          <t>-0.0006179992275009094 +/- 0.0007369171119481795</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-3.862495171881308e-05 +/- 0.0002703746620316916</t>
+          <t>0.00038624951718813083 +/- 0.0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.000502124372344559 +/- 0.0022124377739080065</t>
+          <t>0.003939745075318679 +/- 0.0024232347842963646</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.0016994978756276313 +/- 0.0016586257669821455</t>
+          <t>0.004132869833912733 +/- 0.001954666810178446</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.0030127462340671872 +/- 0.0019755445117874714</t>
+          <t>0.003707995365005834 +/- 0.0008497489378138223</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.862495171879088e-05 +/- 0.0012390123547582367</t>
+          <t>0.00038624951718814194 +/- 0.0013380075763374953</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.0003862495171881086 +/- 0.0017784263318997725</t>
+          <t>-0.0007724990343761839 +/- 0.0006463190625987445</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.0008111239860950304 +/- 0.0005021243723445222</t>
+          <t>0.0011201235998455571 +/- 0.0002703746620316567</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.0030899961375048133 +/- 0.0024550403371294957</t>
+          <t>0.013093858632676748 +/- 0.0023586534786824253</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0.002278872151409805 +/- 0.0022285626476248226</t>
+          <t>-0.0008111239860949748 +/- 0.0023203921662225684</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>-3.8624951718835286e-05 +/- 0.001480399219523893</t>
+          <t>0.0009269988412514806 +/- 0.0012238686379107688</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0030127462340671872 +/- 0.001636896106637079</t>
+          <t>0.011046736191579832 +/- 0.0007369171119482027</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.00019312475859404322 +/- 0.0005253561417047339</t>
+          <t>0.001120123599845535 +/- 0.0006789646902760517</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.00019312475859406542 +/- 0.0009342129488179102</t>
+          <t>-0.002394747006566211 +/- 0.0005676685383043355</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,122 +4161,122 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.0005407493240633277 +/- 0.0018050709069985173</t>
+          <t>0.005832367709540409 +/- 0.0010986066167113409</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.0008883738895326343 +/- 0.002443161776881958</t>
+          <t>0.002162997296253422 +/- 0.0013623168859442582</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>-0.0022402471996910145 +/- 0.0010335332684634645</t>
+          <t>-0.0004248744689068773 +/- 0.0006094914576307242</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-0.0010042487446890625 +/- 0.0009334141346925332</t>
+          <t>0.0012359984550019743 +/- 0.0009107629295134464</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.004055619930475074 +/- 0.002045664376495235</t>
+          <t>-0.0024333719582850023 +/- 0.002533101959377306</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.0007724990343761729 +/- 0.0008636801767090694</t>
+          <t>0.004171494785631558 +/- 0.0013579293805521162</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.0005793742757821407 +/- 0.0005793742757821556</t>
+          <t>-0.000888373889532601 +/- 0.0004586458898044882</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.003089996137504836 +/- 0.0009302120184466738</t>
+          <t>0.0018926226342217412 +/- 0.0013867379738135368</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.001274623406720754 +/- 0.0013385649633961716</t>
+          <t>0.0006179992275010093 +/- 0.001186735534626286</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.0006952491309385689 +/- 0.0010620105897927883</t>
+          <t>-0.002394747006566189 +/- 0.0015333668011803167</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-0.010042487446890725 +/- 0.0019235070835054182</t>
+          <t>-0.0039011201235997885 +/- 0.0008883738895326332</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>-0.00038624951718813083 +/- 0.0022121005891504557</t>
+          <t>0.0007724990343762394 +/- 0.0026082569356715556</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-0.0016994978756276536 +/- 0.0016222479721900369</t>
+          <t>0.001274623406720765 +/- 0.0009930444289055576</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.0016222479721900497 +/- 0.0014738342238964177</t>
+          <t>-0.0024719969100038043 +/- 0.0012716939075438011</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>0.0005407493240633498 +/- 0.00025620894479374493</t>
+          <t>3.862495171884639e-05 +/- 0.0010570824398149065</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>0.011973735032831168 +/- 0.0012926381251974987</t>
+          <t>-0.0008883738895325899 +/- 0.0009625288369545736</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>-0.0018153727307840927 +/- 0.0025034809460175744</t>
+          <t>-0.0008111239860949748 +/- 0.0006094914576307475</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-0.016183854770181572 +/- 0.0011898742217650979</t>
+          <t>-0.000270374662031625 +/- 0.0009469023307942264</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-0.01039011201236002 +/- 0.000781141306147407</t>
+          <t>-0.008149864812668928 +/- 0.000609491457630732</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-0.0002703746620316694 +/- 0.0007338740826573866</t>
+          <t>7.724990343765947e-05 +/- 0.0005933677673131424</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>-0.0009656237929702605 +/- 0.0006045761236963512</t>
+          <t>-7.724990343758176e-05 +/- 0.00037844569220286495</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>-0.0002317497103128785 +/- 0.0003540035299309512</t>
+          <t>-3.862495171879088e-05 +/- 0.00043869512134416336</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-0.018848976438779485 +/- 0.0015906728684413987</t>
+          <t>-0.016106604866743857 +/- 0.0018120825192336509</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-0.0066434916956354065 +/- 0.0013797273927765013</t>
+          <t>-0.008420239474700598 +/- 0.002686031463995929</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4286,92 +4286,92 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-0.0018153727307840927 +/- 0.0009469023307942243</t>
+          <t>-0.0001931247585940099 +/- 0.0006520642339178852</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-0.0038624951718810308 +/- 0.0011842185953461633</t>
+          <t>-0.0013132483584395005 +/- 0.001340235733711675</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-0.012591734260332199 +/- 0.0013947833206077918</t>
+          <t>-0.00996523754345302 +/- 0.0013797273927765024</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.00011587485515642814 +/- 0.0005196455792612624</t>
+          <t>4.4408920985006264e-17 +/- 0.0007529389219628477</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-0.0015836230204712253 +/- 0.0018398617788821362</t>
+          <t>0.001120123599845535 +/- 0.0007005931690698017</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-0.013943607570490558 +/- 0.0013092662229956292</t>
+          <t>-0.013093858632676637 +/- 0.0016876054287333624</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>0.0134801081498648 +/- 0.001919236500394703</t>
+          <t>0.0034762456546929667 +/- 0.0019312475859405297</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>0.002047122441096938 +/- 0.0016929012746860447</t>
+          <t>0.00019312475859409873 +/- 0.0014682563004054213</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>0.0001931247585940543 +/- 0.0003114043162726375</t>
+          <t>-3.862495171880198e-05 +/- 0.00027037466203166146</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.007686365392043237 +/- 0.0014498512459732197</t>
+          <t>0.0005407493240633943 +/- 0.0009801913897605032</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.005330243337195828 +/- 0.0017767477790652624</t>
+          <t>0.000540749324063372 +/- 0.0012480103840404554</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-0.0008111239860950304 +/- 0.0011516455400444603</t>
+          <t>-0.0004248744689068551 +/- 0.0005845015817080366</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.012282734646581672 +/- 0.002162997296253378</t>
+          <t>0.01243723445345699 +/- 0.0013468980899314547</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>0.00799536500579372 +/- 0.0008816309162235088</t>
+          <t>0.005832367709540398 +/- 0.0011898742217651102</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>0.0030127462340671985 +/- 0.0017513764463120392</t>
+          <t>-0.0007724990343761839 +/- 0.0012335820334238071</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>-0.0006566241792198002 +/- 0.0003016705166437331</t>
+          <t>3.862495171881308e-05 +/- 0.00011587485515643923</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>-7.724990343763727e-05 +/- 0.0007686268343813239</t>
+          <t>-3.8624951718768676e-05 +/- 0.0005583944493936219</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>0.0006566241792197558 +/- 0.0005996204981174145</t>
+          <t>0.0007338740826574375 +/- 0.00043869512134418</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>0.0005021243723445145 +/- 0.0011333642913187443</t>
+          <t>0.00030899961375052687 +/- 0.0009107629295134352</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>0.01116261104673616 +/- 0.002167475912954521</t>
+          <t>0.005098493626882994 +/- 0.0006179992275009677</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4396,37 +4396,37 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>-0.0002703746620316805 +/- 0.0005196455792612658</t>
+          <t>-0.00023174971031280077 +/- 0.0008497489378138232</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.003321745847817692 +/- 0.0012716939075438018</t>
+          <t>0.0005793742757821852 +/- 0.0010255633872036716</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0.002124372344534553 +/- 0.001362864330967737</t>
+          <t>0.004248744689069173 +/- 0.0012926381251975121</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>-0.0028968713789107926 +/- 0.0010400086533670439</t>
+          <t>-0.0025492468134414416 +/- 0.0009008809416524237</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>0.007377365778292755 +/- 0.0020398216958687912</t>
+          <t>0.0039011201235998995 +/- 0.0018235722880050789</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>0.005098493626882949 +/- 0.0023671770484425857</t>
+          <t>0.004596369254538479 +/- 0.0012978213685910771</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>0.0012746234067207208 +/- 0.0013606732293401902</t>
+          <t>0.002162997296253422 +/- 0.0012949443502696272</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.0007334066740007694 +/- 0.0019404116692809557</t>
+          <t>-0.006160616061606128 +/- 0.0021306694604083616</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.010047671433810024 +/- 0.0014409154898708165</t>
+          <t>-0.008397506417308376 +/- 0.0026313360030671444</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.0016134946828016306 +/- 0.0025574764611899863</t>
+          <t>-0.0013201320132012807 +/- 0.001941797182966427</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.0028602860286028762 +/- 0.0028252820365615313</t>
+          <t>-0.009974330766409956 +/- 0.0015101767716885876</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.005243857719105216 +/- 0.0018987302480380861</t>
+          <t>-0.004033736707003988 +/- 0.0017814386214141744</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.006123945727906155 +/- 0.0020876340781063926</t>
+          <t>-0.011404473780711365 +/- 0.0031734143214257465</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0005500550055005049 +/- 0.0004415692914848734</t>
+          <t>-0.00033003300330033405 +/- 0.0002566923359002422</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.019361936193619412 +/- 0.002155766550304242</t>
+          <t>-0.027502750275027486 +/- 0.001766277165939468</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.040190685735240164 +/- 0.00436114961417485</t>
+          <t>0.03289328932893293 +/- 0.004530085075979164</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.04345434543454341 +/- 0.0037798914792974542</t>
+          <t>0.027722772277227747 +/- 0.004354978464042102</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.002456912357902419 +/- 0.001954566625777267</t>
+          <t>-0.0022368903557022147 +/- 0.0014338991416220836</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.00088008800880085 +/- 0.0018349829120934123</t>
+          <t>0.005097176384305113 +/- 0.0014800466498430904</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-0.004143747708104173 +/- 0.0034635513575704663</t>
+          <t>-0.008874220755408835 +/- 0.0031579098117507955</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.012761276127612742 +/- 0.0025448260466296294</t>
+          <t>0.009827649431609842 +/- 0.0027627148077502568</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>-0.007517418408507548 +/- 0.0029071504181119967</t>
+          <t>0.0048404840484048695 +/- 0.002658535967787577</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>-0.01672167216721676 +/- 0.0015832074180361561</t>
+          <t>-0.027722772277227702 +/- 0.0017904738710280517</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.002933626696002889 +/- 0.001926501728868884</t>
+          <t>-0.0022368903557022147 +/- 0.0022512717973114356</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-0.010854418775210895 +/- 0.003464133679096313</t>
+          <t>-0.01279794646131278 +/- 0.002269120426022003</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.003557022368903595 +/- 0.0025302530253025353</t>
+          <t>-0.0035203520352035 +/- 0.001729347432717514</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.0008067473414007708 +/- 0.00042764590354568954</t>
+          <t>-7.334066740006806e-05 +/- 0.0003196845576487501</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.01177117711771175 +/- 0.0018944761794044002</t>
+          <t>0.011441144114411462 +/- 0.0021682061604832424</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.004033736707003998 +/- 0.001124291141676265</t>
+          <t>7.334066740007916e-05 +/- 0.0016051388799588854</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.0016868353502016652 +/- 0.0011848547430439184</t>
+          <t>-0.00029336266960027223 +/- 0.0014371777002028221</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.0015401540154014847 +/- 0.00139925075382026</t>
+          <t>-0.0001833516685001646 +/- 0.0014320223094805085</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.0012467913458012124 +/- 0.0014502178168892914</t>
+          <t>-0.0030803080308030363 +/- 0.0012724130233148158</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.0001833516685001646 +/- 0.00047103896511422266</t>
+          <t>-0.001136780344701105 +/- 0.0007416116030860583</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>-0.010121012101210136 +/- 0.0039262952150565964</t>
+          <t>-0.012321232123212289 +/- 0.002788874710939724</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.01177117711771174 +/- 0.00307877972109313</t>
+          <t>0.0015034836817015452 +/- 0.0018513979554623259</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0.0017601760176017445 +/- 0.0017799282874237789</t>
+          <t>-0.0036303630363035966 +/- 0.0011989572955094776</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.009130913091309156 +/- 0.0020048312332726858</t>
+          <t>-0.015768243491015733 +/- 0.0021319313316829807</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>-0.00022002200220027078 +/- 0.0006393691152975025</t>
+          <t>-0.00022002200220020419 +/- 0.0008861786559291678</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.00025669233590029926 +/- 0.0005692766665295056</t>
+          <t>0.0004400440044004639 +/- 0.0006721783197588325</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,122 +4606,122 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.00047671433810043685 +/- 0.0012602009737762967</t>
+          <t>-0.015291529152915262 +/- 0.002689963320145723</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.01276127612761272 +/- 0.0029872257945605185</t>
+          <t>0.008690869086908715 +/- 0.0023767921412686235</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>-0.00029336266960032774 +/- 0.0003196845576487501</t>
+          <t>-0.0019801980198019486 +/- 0.0005958223985798334</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.0012467913458012124 +/- 0.0007185888501014083</t>
+          <t>0.0009534286762009625 +/- 0.000972973902561182</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.002163549688302202 +/- 0.0020708189077367554</t>
+          <t>-0.003667033370003647 +/- 0.0013119577425741325</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>0.003263659699303223 +/- 0.00178483220002023</t>
+          <t>0.00381371470480385 +/- 0.0014686457201687376</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>0.00022002200220017087 +/- 0.0007550883858443125</t>
+          <t>0.0017601760176017777 +/- 0.0009534286762009429</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.009387605427209345 +/- 0.001354322355160945</t>
+          <t>-0.0009534286762009292 +/- 0.0009866977665620384</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.0056839017235056355 +/- 0.001505271415604963</t>
+          <t>-0.0003300330033003118 +/- 0.001977819810804813</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-0.007700770077007746 +/- 0.0014668133480014612</t>
+          <t>-0.00964429776310961 +/- 0.0018701870187018566</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.002090209020902056 +/- 0.0028264716791409007</t>
+          <t>-0.006453978731206411 +/- 0.0022136249758396135</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.00396039603960392 +/- 0.0017027043294820538</t>
+          <t>0.0021268793546021514 +/- 0.001670815658217022</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0028236156949027922 +/- 0.001382330533551212</t>
+          <t>-0.0004033736707003799 +/- 0.0018072932204402665</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.005390539053905419 +/- 0.001581932864695476</t>
+          <t>0.0006233956729006396 +/- 0.0014764079310008887</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.0008800880088008278 +/- 0.0006179794479777297</t>
+          <t>0.0005867253392006111 +/- 0.0007726918777303063</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>-0.001100110011001132 +/- 0.0008521415503206645</t>
+          <t>-0.002933626696002889 +/- 0.0012596673294695759</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>-0.012761276127612797 +/- 0.0015712713814175778</t>
+          <t>-0.00513384671800512 +/- 0.001656265462506235</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-0.0031169783645031536 +/- 0.0019900203228771754</t>
+          <t>-0.012137880454712114 +/- 0.0023620363645307026</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-0.008764209754308794 +/- 0.001799837358534353</t>
+          <t>-0.014301430143014294 +/- 0.0015644099015549502</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>0.0015034836817014563 +/- 0.0006014381909371706</t>
+          <t>-0.0004400440044004195 +/- 0.0007830640448867794</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>-0.0011367803447011715 +/- 0.000794147701786122</t>
+          <t>-0.0016501650165016257 +/- 0.0008075803280361277</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>-0.000770077007700809 +/- 0.0005301368644958234</t>
+          <t>-7.334066740006806e-05 +/- 0.0003196845576487501</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-0.0014301430143014659 +/- 0.0023790541376323615</t>
+          <t>0.0013201320132013362 +/- 0.0020626858981188574</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.006123945727906111 +/- 0.0011717304956854065</t>
+          <t>0.00425375870920427 +/- 0.0011848547430439013</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4731,92 +4731,92 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>0.00011001100110006324 +/- 0.0008042432049674069</t>
+          <t>0.0001833516685001868 +/- 0.0006190664839066354</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>0.007444077741107402 +/- 0.0013021841514165382</t>
+          <t>0.00029336266960031663 +/- 0.0020924594965437597</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-0.014008067473414054 +/- 0.0022353869679689405</t>
+          <t>-0.0020902090209020787 +/- 0.0023253155647213397</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>-0.0008800880088009166 +/- 0.000930588745174158</t>
+          <t>-0.000806747341400782 +/- 0.0007656990472248296</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-0.0009167583425009673 +/- 0.001014251315433749</t>
+          <t>-0.005940594059405913 +/- 0.002105273207833847</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-0.004620462046204666 +/- 0.00269570604319607</t>
+          <t>0.0023835716905024062 +/- 0.0015665573423757884</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-0.0015034836817015452 +/- 0.002894169933608442</t>
+          <t>0.001503483681701534 +/- 0.001746755462239028</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-0.007040704070407078 +/- 0.0023180756331909096</t>
+          <t>0.002566923359002604 +/- 0.0012051101375251257</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>7.334066740005696e-05 +/- 0.00027441564992839845</t>
+          <t>0.0002200220022002375 +/- 0.0002933626696003167</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>-0.0017235056839017492 +/- 0.0017590296964006499</t>
+          <t>-0.0009167583425009118 +/- 0.0019628050885328184</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>-0.007957462412907979 +/- 0.0015034836817014918</t>
+          <t>0.004913824715804938 +/- 0.0009866977665620583</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.004693802713604667 +/- 0.0013201320132013162</t>
+          <t>0.003226989365603239 +/- 0.0011572962110787894</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.003593692702603557 +/- 0.0026023021634338484</t>
+          <t>0.0013568023469013868 +/- 0.002421630653626553</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>0.00029336266960027223 +/- 0.002086023124800573</t>
+          <t>-0.0010267693436009973 +/- 0.001802450418400373</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>0.0006233956729005841 +/- 0.001841201351027966</t>
+          <t>0.00781078107810782 +/- 0.0016485344182610223</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>0.00011001100110006324 +/- 0.0006147068065361338</t>
+          <t>-0.0003667033370003514 +/- 0.0004919841534652897</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.0003667033370003181 +/- 0.0006957706623032823</t>
+          <t>7.334066740009027e-05 +/- 0.0007297304269208811</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>0.0016868353502016652 +/- 0.0007370645853407437</t>
+          <t>0.000916758342500923 +/- 0.000661083842219296</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4826,52 +4826,52 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>0.0011734506784011334 +/- 0.0008000522269626532</t>
+          <t>0.000843417675100866 +/- 0.0007700770077007847</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>-0.0013934726806014263 +/- 0.0019733955331241245</t>
+          <t>0.0043270993766043485 +/- 0.0011916447971596497</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>-3.6670333700050685e-05 +/- 0.00019747579050730888</t>
+          <t>0.0 +/- 0.0001639947178217798</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.001943527686101898 +/- 0.0007524123406191092</t>
+          <t>0.001906857352401936 +/- 0.0006721783197588325</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>-0.00795746241290799 +/- 0.0019198592024508028</t>
+          <t>-0.006453978731206433 +/- 0.0006996253769101373</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>-0.0005500550055005937 +/- 0.0019212595375767685</t>
+          <t>-0.005023835716905012 +/- 0.0015562226016811896</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>0.0016868353502016542 +/- 0.0009866977665620698</t>
+          <t>0.000513384671800532 +/- 0.0010267693436010203</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>-0.007334066740007372 +/- 0.0016804457993970714</t>
+          <t>0.0023469013568023778 +/- 0.0010526366039169605</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>-0.000770077007700809 +/- 0.001452534090233846</t>
+          <t>-0.004107077374404089 +/- 0.0027965787994041137</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>-0.0016501650165016701 +/- 0.0016172407092922487</t>
+          <t>0.005537220388705566 +/- 0.0010684856827527331</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-0.0015696784073506499 +/- 0.0007742629562081364</t>
+          <t>-0.0031393568147014108 +/- 0.0015485259124162838</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,157 +4891,157 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.008575803981623243 +/- 0.002348830268021128</t>
+          <t>0.004173047473200598 +/- 0.0012399796891808305</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.002947932618683047 +/- 0.0013595161488946916</t>
+          <t>0.001033690658499209 +/- 0.0014329990254374337</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.009073506891271 +/- 0.0010136448924099276</t>
+          <t>-0.0006508422664624925 +/- 0.0011991163677922071</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0011485451761102828 +/- 0.0015785243589654095</t>
+          <t>0.007580398162327684 +/- 0.001171290853045804</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.006470137825421174 +/- 0.0013201332044078665</t>
+          <t>0.004211332312404281 +/- 0.0014324875140788336</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.00015313935681467993 +/- 0.00025395289359536616</t>
+          <t>0.0007274119448698269 +/- 0.000604124572666914</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.00562787136294024 +/- 0.00162473929356224</t>
+          <t>-0.0034456355283307817 +/- 0.00132622573320741</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.009303215926493158 +/- 0.0017714755438375752</t>
+          <t>0.008575803981623253 +/- 0.0020631230605371136</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.012289433384379721 +/- 0.0032775489626071263</t>
+          <t>0.019908116385911157 +/- 0.0030723434376322928</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.004670750382848432 +/- 0.0007423705754083305</t>
+          <t>0.004747320061255711 +/- 0.001976031837758651</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-0.001569678407350661 +/- 0.0011669028065947943</t>
+          <t>0.002641653905053587 +/- 0.00179938744257276</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.00428790199081166 +/- 0.0010664922111167066</t>
+          <t>0.012251148545176106 +/- 0.002082920445441873</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.02660796324655441 +/- 0.0030157665533396285</t>
+          <t>0.03774885145482385 +/- 0.0032313855813184147</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.004096477794793285 +/- 0.001161867603789705</t>
+          <t>0.007235834609494618 +/- 0.002763147101954986</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>-0.0027182235834609103 +/- 0.0015919313082918554</t>
+          <t>-0.0006891271056661763 +/- 0.0013240135119288168</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.0023736600306278554 +/- 0.0011837385018177774</t>
+          <t>-0.0014165390505360143 +/- 0.0015414105772739491</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-0.0021439509954057747 +/- 0.0010158115743814403</t>
+          <t>-0.004287901990811671 +/- 0.0015766661777927965</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0.0004211332312404559 +/- 0.0008291120914130192</t>
+          <t>0.001378254211332286 +/- 0.0011382901031637515</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3.828483920368386e-05 +/- 0.00011485451761105159</t>
+          <t>-0.00019142419601837491 +/- 0.0003086622415121954</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.002220520673813209 +/- 0.001987864469486553</t>
+          <t>0.0071209800918835995 +/- 0.0027671226645624414</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-0.00133996937212858 +/- 0.0013830315366147388</t>
+          <t>3.8284839203661655e-05 +/- 0.0018868639403294722</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>-0.0016845329249616681 +/- 0.0012835417009372271</t>
+          <t>-0.009800918836140916 +/- 0.0009865312960739094</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.0016079632465544114 +/- 0.0009655069075741411</t>
+          <t>-0.0035222052067381713 +/- 0.0006360355178344659</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.0006508422664624258 +/- 0.0011102603369065815</t>
+          <t>0.006738131699846839 +/- 0.0019981605437519125</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.00022970903522202547 +/- 0.0002539528935953695</t>
+          <t>0.0006508422664624813 +/- 0.0006642171352564129</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.00011485451761106269 +/- 0.0012352424046632238</t>
+          <t>-0.004326186830015344 +/- 0.002585573354502775</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0.0022970903522205543 +/- 0.0009377832093350607</t>
+          <t>-0.0061255742725880745 +/- 0.0022389267254538116</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0.0014165390505360253 +/- 0.0008396520750176833</t>
+          <t>-0.0022588055130168703 +/- 0.0012749483771322264</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.0016079632465543115 +/- 0.001718985016894596</t>
+          <t>0.0003445635528330548 +/- 0.0026769289596345115</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0011868300153139665 +/- 0.0003180177589172096</t>
+          <t>0.0003828483920367387 +/- 0.00038284839203674983</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.00011485451761104049 +/- 0.000245142581831298</t>
+          <t>0.0004594180704440731 +/- 0.00041234033745284385</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,122 +5051,122 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.0065849923430321144 +/- 0.0019203577647755763</t>
+          <t>0.007810107197549754 +/- 0.0020702152886057775</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.0011485451761103049 +/- 0.0010272900356048213</t>
+          <t>-0.0001914241960184082 +/- 0.0013179107563597741</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>3.828483920370607e-05 +/- 0.00026799387442575214</t>
+          <t>-0.0005359877488514741 +/- 0.00025395289359539294</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.0008422664624809118 +/- 0.0005881428597142922</t>
+          <t>0.00126339969372129 +/- 0.0005150698333489202</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.0024885145482388517 +/- 0.001086237439441891</t>
+          <t>-0.009188361408882096 +/- 0.0016061391243034453</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>0.0022588055130168816 +/- 0.0007354277454938136</t>
+          <t>0.006699846860643166 +/- 0.0015808440139404643</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.0007656967840735552 +/- 0.0005414293883510954</t>
+          <t>0.0003828483920367387 +/- 0.0005414293883510954</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.000803981623277128 +/- 0.0010336906584992303</t>
+          <t>-0.0019142419601837824 +/- 0.0011985050415389668</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>7.656967840738993e-05 +/- 0.0010100234271265634</t>
+          <t>-0.00643185298621749 +/- 0.0015579624769813017</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>4.4408920985006264e-17 +/- 0.0010129216351702096</t>
+          <t>-0.003598774885145495 +/- 0.0019908116385911217</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-0.013973966309341468 +/- 0.001748154679453403</t>
+          <t>-0.01010719754977033 +/- 0.0012130918466887357</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.0010719754977029593 +/- 0.001399361935872673</t>
+          <t>-0.007848392036753471 +/- 0.0017313046025413605</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.00042113323124047807 +/- 0.0009291470979717942</t>
+          <t>-0.003713629402756535 +/- 0.001293211772898506</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4.4408920985006264e-17 +/- 0.001246464057894309</t>
+          <t>-0.0013399693721286576 +/- 0.0014653644111029785</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>0.00045941807044416196 +/- 0.0003751132837340261</t>
+          <t>-0.0012251148545176394 +/- 0.0008696643714854985</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>0.0006508422664625368 +/- 0.0011102603369065817</t>
+          <t>-0.007656967840735085 +/- 0.002054580071209612</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.00034456355283312145 +/- 0.0009753245943994659</t>
+          <t>-0.010681470137825444 +/- 0.0018868639403294871</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-0.0028713629402756123 +/- 0.0014950707649132116</t>
+          <t>-0.002641653905053609 +/- 0.002050652640251467</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.0026416539050536426 +/- 0.0011285913455576966</t>
+          <t>0.000650842266462448 +/- 0.0015126145685404712</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>0.00045941807044416196 +/- 0.00028649750281578513</t>
+          <t>0.0014548238897396538 +/- 0.0011201178283558827</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.0002679938744257648 +/- 0.0007274119448698262</t>
+          <t>0.0032159264931087006 +/- 0.0013394223341911158</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.0001914241960184193 +/- 0.0001914241960184193</t>
+          <t>-0.00042113323124043367 +/- 0.0005263295208601759</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.0018759571209801319 +/- 0.0010753883541491651</t>
+          <t>0.0042879019908116265 +/- 0.0018582941959435972</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-0.028637059724349136 +/- 0.002171125096287576</t>
+          <t>-0.011983154670750406 +/- 0.0019674831787947185</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5176,92 +5176,92 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>0.0003062787136294487 +/- 0.000286497502815797</t>
+          <t>0.002833078101071951 +/- 0.0007695157443430981</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-0.002411944869831495 +/- 0.0010561343203777667</t>
+          <t>-0.003598774885145517 +/- 0.0012835417009372252</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-0.009762633996937164 +/- 0.0013179107563597724</t>
+          <t>-0.011600306278713645 +/- 0.001597446098393953</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.0005359877488514964 +/- 0.000459418070444112</t>
+          <t>0.0006508422664624703 +/- 0.0010280031839278335</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-0.0016079632465543225 +/- 0.0011587094908439223</t>
+          <t>-0.006278713629402788 +/- 0.0007883330888963999</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-0.004211332312404248 +/- 0.0012106729173692102</t>
+          <t>-0.010490045941807058 +/- 0.0020843273489764393</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>0.000995405819295614 +/- 0.0006891271056661616</t>
+          <t>0.0011868300153139333 +/- 0.0008291120914130131</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-0.010681470137825366 +/- 0.0016727451971633737</t>
+          <t>-0.004632465543644737 +/- 0.0016193174565510397</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>0.00022970903522209207 +/- 0.00025395289359539294</t>
+          <t>0.00011485451761101828 +/- 0.00017544317362004326</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>-0.0026416539050535424 +/- 0.0010049314508733939</t>
+          <t>-0.010183767228177654 +/- 0.0012488136623506907</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>-0.0024885145482388517 +/- 0.0016355290477253848</t>
+          <t>-0.0056661562021439685 +/- 0.0016493613498114608</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-0.0011485451761102273 +/- 0.000513645017802417</t>
+          <t>-0.0003445635528330993 +/- 0.0013421552942540717</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-0.002411944869831506 +/- 0.0012818276449298002</t>
+          <t>-0.007312404287902008 +/- 0.0019176845002095353</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>-0.0021056661562020907 +/- 0.0019313933010152253</t>
+          <t>-0.002871362940275679 +/- 0.002091698067327368</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>-0.001875957120980032 +/- 0.0011415047102508017</t>
+          <t>-0.005015313935681498 +/- 0.0012977374622265088</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>-0.0003828483920367276 +/- 0.00017121500593412242</t>
+          <t>-0.0003062787136293932 +/- 0.00022970903522205878</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>-0.00022970903522201436 +/- 0.0005468168781426258</t>
+          <t>0.0011868300153139333 +/- 0.00094479040423071</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>-7.656967840731221e-05 +/- 0.00129037515668859</t>
+          <t>0.001225114854517595 +/- 0.0006360355178344646</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>0.0009188361408882572 +/- 0.0003508863472400865</t>
+          <t>0.0008805513016845401 +/- 0.0007274119448698303</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>-0.006163859111791692 +/- 0.0006944240868000339</t>
+          <t>-0.015543644716692206 +/- 0.0014242783489845424</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5286,37 +5286,37 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>-0.0004211332312404004 +/- 0.0005534774998009567</t>
+          <t>-0.00026799387442573154 +/- 0.00038475787217155286</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>-0.00015313935681463554 +/- 0.0010719754977029244</t>
+          <t>0.010949464012251142 +/- 0.001071975497702922</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>-0.0013016845329249182 +/- 0.0010855625481437793</t>
+          <t>-0.014318529862174578 +/- 0.002220520673813158</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>0.0008422664624808896 +/- 0.0009346520379581863</t>
+          <t>-0.00042113323124043367 +/- 0.0007152198197652886</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>0.00034456355283312145 +/- 0.0011285913455577176</t>
+          <t>-0.0011868300153139444 +/- 0.0016814847822356554</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>-0.007465543644716644 +/- 0.0010996482860907532</t>
+          <t>-0.011676875957121002 +/- 0.0018220526851900093</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>0.0026416539050536534 +/- 0.0006279180500327781</t>
+          <t>-0.002718223583460977 +/- 0.0016193174565510215</t>
         </is>
       </c>
     </row>
